--- a/data/posts.xlsx
+++ b/data/posts.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59E49219-63E9-4F12-BCD4-DE29211C265B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AEB5FE0-6315-4D55-9744-13D721A453A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9230" yWindow="1310" windowWidth="28800" windowHeight="15450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="107">
   <si>
     <t>date</t>
   </si>
@@ -346,6 +346,12 @@
   </si>
   <si>
     <t>https://www.linkedin.com/posts/kasparrufibach_biostatistics-adaptive-innovation-activity-7357467143770107904-z2iF?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAAQJ2qsB_r_XsYhAPWyf_WQeC5V6NOcbIXo</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/posts/kasparrufibach_biostatistics-collaboration-activity-7377702182470443008-EFvl?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAAQJ2qsB_r_XsYhAPWyf_WQeC5V6NOcbIXo</t>
+  </si>
+  <si>
+    <t>EORTC one-day event on p-values</t>
   </si>
 </sst>
 </file>
@@ -688,17 +694,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E50"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:E51"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="106.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="106.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="223" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="99.36328125" customWidth="1"/>
+    <col min="5" max="5" width="99.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -715,706 +721,720 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
+        <v>45927</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
         <v>45871</v>
       </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
         <v>103</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="2">
+    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
         <v>45868</v>
       </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="2">
+    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
         <v>45855</v>
       </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="5" t="s">
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D5" t="s">
         <v>99</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E5" s="4" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="2">
+    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
         <v>45784</v>
       </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
         <v>96</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D6" t="s">
         <v>97</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="2">
+    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
         <v>45725</v>
       </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
         <v>94</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D7" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="2">
+    <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
         <v>45696</v>
       </c>
-      <c r="B7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
         <v>93</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="2">
+    <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
         <v>45686</v>
       </c>
-      <c r="B8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
         <v>90</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="2">
+    <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
         <v>45623</v>
       </c>
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" t="s">
         <v>89</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D10" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
         <v>45584</v>
       </c>
-      <c r="B10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" t="s">
         <v>87</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D11" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
         <v>45568</v>
       </c>
-      <c r="B11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="5" t="s">
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D12" t="s">
         <v>83</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E12" s="4" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
         <v>45565</v>
       </c>
-      <c r="B12" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" t="s">
         <v>82</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D13" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
         <v>45557</v>
       </c>
-      <c r="B13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="B14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" t="s">
         <v>79</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D14" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
         <v>45537</v>
       </c>
-      <c r="B14" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="B15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" t="s">
         <v>77</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D15" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
         <v>45533</v>
       </c>
-      <c r="B15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="B16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" t="s">
         <v>75</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D16" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
         <v>45509</v>
       </c>
-      <c r="B16" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="B17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" t="s">
         <v>71</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D17" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="2">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
         <v>45504</v>
       </c>
-      <c r="B17" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="B18" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" t="s">
         <v>73</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D18" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" s="2">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
         <v>45490</v>
       </c>
-      <c r="B18" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="B19" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" t="s">
         <v>69</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D19" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" s="2">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
         <v>45482</v>
       </c>
-      <c r="B19" t="s">
-        <v>22</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="B20" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" t="s">
         <v>67</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D20" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" s="2">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
         <v>45473</v>
       </c>
-      <c r="B20" t="s">
-        <v>22</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="B21" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" t="s">
         <v>65</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D21" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" s="2">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
         <v>45443</v>
       </c>
-      <c r="B21" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="B22" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" t="s">
         <v>63</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D22" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A22" s="2">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
         <v>45357</v>
       </c>
-      <c r="B22" t="s">
-        <v>22</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="B23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" t="s">
         <v>60</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D23" t="s">
         <v>61</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E23" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A23" s="2">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
         <v>45352</v>
       </c>
-      <c r="B23" t="s">
-        <v>22</v>
-      </c>
-      <c r="C23" t="s">
+      <c r="B24" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" t="s">
         <v>59</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D24" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A24" s="2">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
         <v>45240</v>
       </c>
-      <c r="B24" t="s">
-        <v>22</v>
-      </c>
-      <c r="C24" t="s">
+      <c r="B25" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25" t="s">
         <v>57</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D25" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A25" s="2">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
         <v>45212</v>
       </c>
-      <c r="B25" t="s">
-        <v>22</v>
-      </c>
-      <c r="C25" t="s">
+      <c r="B26" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" t="s">
         <v>53</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D26" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A26" s="2">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
         <v>45211</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C26" t="s">
+      <c r="B27" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C27" t="s">
         <v>51</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D27" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A27" s="2">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
         <v>45147</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C27" t="s">
+      <c r="B28" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" t="s">
         <v>47</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D28" t="s">
         <v>48</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E28" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A28" s="2">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
         <v>45143</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C28" t="s">
+      <c r="B29" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29" t="s">
         <v>44</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D29" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A29" s="2">
+    <row r="30" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A30" s="2">
         <v>45119</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C29" s="3" t="s">
+      <c r="B30" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D30" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A30" s="2">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
         <v>45113</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C30" t="s">
+      <c r="B31" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C31" t="s">
         <v>26</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D31" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A31" s="2">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
         <v>45112</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C31" t="s">
+      <c r="B32" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C32" t="s">
         <v>28</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D32" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A32" s="2">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
         <v>45083</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C32" t="s">
+      <c r="B33" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C33" t="s">
         <v>12</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D33" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" s="2">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
         <v>45082</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C33" t="s">
+      <c r="B34" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C34" t="s">
         <v>13</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D34" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" s="2">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
         <v>45018</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C34" t="s">
+      <c r="B35" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C35" t="s">
         <v>54</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D35" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" s="2">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
         <v>45014</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C35" t="s">
+      <c r="B36" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C36" t="s">
         <v>14</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D36" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" s="2">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
         <v>44992</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C36" t="s">
+      <c r="B37" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C37" t="s">
         <v>15</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D37" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" s="2">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
         <v>44959</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C37" t="s">
+      <c r="B38" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C38" t="s">
         <v>16</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D38" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" s="2">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="2">
         <v>44930</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C38" t="s">
+      <c r="B39" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C39" t="s">
         <v>17</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D39" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" s="2">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
         <v>44897</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C39" t="s">
+      <c r="B40" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C40" t="s">
         <v>18</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="D40" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" s="2">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="2">
         <v>44682</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C40" t="s">
+      <c r="B41" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" t="s">
         <v>19</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D41" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" s="2">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
         <v>44601</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C41" t="s">
+      <c r="B42" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C42" t="s">
         <v>20</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D42" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" s="2">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="2">
         <v>44725</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C42" t="s">
-        <v>40</v>
-      </c>
-      <c r="D42" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" s="2">
-        <v>44723</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C43" t="s">
-        <v>42</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+        <v>40</v>
+      </c>
+      <c r="D43" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
-        <v>44326</v>
+        <v>44723</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C44" t="s">
-        <v>38</v>
-      </c>
-      <c r="D44" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+        <v>42</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
-        <v>44265</v>
+        <v>44326</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C45" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D45" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
-        <v>44148</v>
+        <v>44265</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C46" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D46" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
-        <v>44146</v>
+        <v>44148</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C47" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D47" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
-        <v>44144</v>
+        <v>44146</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C48" t="s">
+        <v>32</v>
+      </c>
+      <c r="D48" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="2">
+        <v>44144</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C49" t="s">
         <v>31</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D49" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B49" s="2"/>
-    </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B50" s="2"/>
     </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B51" s="2"/>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A19:D39">
-    <sortCondition ref="B19:B39"/>
-    <sortCondition descending="1" ref="A19:A39"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A20:D40">
+    <sortCondition ref="B20:B40"/>
+    <sortCondition descending="1" ref="A20:A40"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="D39" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="D29" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="D30" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="D31" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="D43" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="D26" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="D34" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="D18" r:id="rId8" xr:uid="{FA3531C4-3B8B-4257-B20B-BB3BF511A818}"/>
-    <hyperlink ref="E11" r:id="rId9" xr:uid="{461EAE59-6B89-4B06-BC7F-5D62D70EDCD6}"/>
-    <hyperlink ref="D8" r:id="rId10" xr:uid="{9FC614FC-A94D-4784-8E8F-DFD619EA88C0}"/>
-    <hyperlink ref="D7" r:id="rId11" xr:uid="{0B29772C-F7FE-40CC-A257-2848F4518174}"/>
-    <hyperlink ref="E5" r:id="rId12" xr:uid="{C474B74F-3E03-433F-BC35-18768486A4FB}"/>
-    <hyperlink ref="E4" r:id="rId13" xr:uid="{209BE10C-36A4-4475-BDA6-365C34A7A7B4}"/>
-    <hyperlink ref="D3" r:id="rId14" xr:uid="{D908A389-6872-41E0-B81F-166FB55D55A3}"/>
-    <hyperlink ref="D2" r:id="rId15" xr:uid="{1BBDB9F5-EA33-4B8D-A13B-752105B1611A}"/>
+    <hyperlink ref="D40" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="D30" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="D31" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="D32" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="D44" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="D27" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="D35" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="D19" r:id="rId8" xr:uid="{FA3531C4-3B8B-4257-B20B-BB3BF511A818}"/>
+    <hyperlink ref="E12" r:id="rId9" xr:uid="{461EAE59-6B89-4B06-BC7F-5D62D70EDCD6}"/>
+    <hyperlink ref="D9" r:id="rId10" xr:uid="{9FC614FC-A94D-4784-8E8F-DFD619EA88C0}"/>
+    <hyperlink ref="D8" r:id="rId11" xr:uid="{0B29772C-F7FE-40CC-A257-2848F4518174}"/>
+    <hyperlink ref="E6" r:id="rId12" xr:uid="{C474B74F-3E03-433F-BC35-18768486A4FB}"/>
+    <hyperlink ref="E5" r:id="rId13" xr:uid="{209BE10C-36A4-4475-BDA6-365C34A7A7B4}"/>
+    <hyperlink ref="D4" r:id="rId14" xr:uid="{D908A389-6872-41E0-B81F-166FB55D55A3}"/>
+    <hyperlink ref="D3" r:id="rId15" xr:uid="{1BBDB9F5-EA33-4B8D-A13B-752105B1611A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId16"/>

--- a/data/posts.xlsx
+++ b/data/posts.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AEB5FE0-6315-4D55-9744-13D721A453A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3E6C842-2D9D-43E2-97A0-27070F519647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="109">
   <si>
     <t>date</t>
   </si>
@@ -352,6 +352,12 @@
   </si>
   <si>
     <t>EORTC one-day event on p-values</t>
+  </si>
+  <si>
+    <t>Nine questions about stratification and covariate adjustment: Part 1</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/posts/kasparrufibach_in-virtually-all-clinical-trials-we-stratify-activity-7382149707659153408-lEbc?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAAQJ2qsB_r_XsYhAPWyf_WQeC5V6NOcbIXo</t>
   </si>
 </sst>
 </file>
@@ -694,7 +700,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -723,718 +729,732 @@
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
-        <v>45927</v>
+        <v>45941</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
-        <v>45871</v>
+        <v>45927</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>103</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
+      </c>
+      <c r="D3" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
-        <v>45868</v>
+        <v>45871</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
-        <v>45855</v>
+        <v>45868</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="D5" t="s">
-        <v>99</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>84</v>
+      <c r="C5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>45784</v>
+        <v>45855</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
       </c>
-      <c r="C6" t="s">
-        <v>96</v>
+      <c r="C6" s="5" t="s">
+        <v>100</v>
       </c>
       <c r="D6" t="s">
-        <v>97</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <v>45725</v>
+        <v>45784</v>
       </c>
       <c r="B7" t="s">
         <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D7" t="s">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>45696</v>
+        <v>45725</v>
       </c>
       <c r="B8" t="s">
         <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
+      </c>
+      <c r="D8" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>45686</v>
+        <v>45696</v>
       </c>
       <c r="B9" t="s">
         <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
+        <v>45686</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" t="s">
+        <v>90</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
         <v>45623</v>
       </c>
-      <c r="B10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" t="s">
         <v>89</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D11" t="s">
         <v>88</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
-        <v>45584</v>
-      </c>
-      <c r="B11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" t="s">
-        <v>87</v>
-      </c>
-      <c r="D11" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
-        <v>45568</v>
+        <v>45584</v>
       </c>
       <c r="B12" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>85</v>
+      <c r="C12" t="s">
+        <v>87</v>
       </c>
       <c r="D12" t="s">
-        <v>83</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
-        <v>45565</v>
+        <v>45568</v>
       </c>
       <c r="B13" t="s">
         <v>22</v>
       </c>
-      <c r="C13" t="s">
-        <v>82</v>
+      <c r="C13" s="5" t="s">
+        <v>85</v>
       </c>
       <c r="D13" t="s">
-        <v>81</v>
+        <v>83</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <v>45557</v>
+        <v>45565</v>
       </c>
       <c r="B14" t="s">
         <v>22</v>
       </c>
       <c r="C14" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
-        <v>45537</v>
+        <v>45557</v>
       </c>
       <c r="B15" t="s">
         <v>22</v>
       </c>
       <c r="C15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D15" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
-        <v>45533</v>
+        <v>45537</v>
       </c>
       <c r="B16" t="s">
         <v>22</v>
       </c>
       <c r="C16" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D16" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
-        <v>45509</v>
+        <v>45533</v>
       </c>
       <c r="B17" t="s">
         <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D17" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
-        <v>45504</v>
+        <v>45509</v>
       </c>
       <c r="B18" t="s">
         <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D18" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
-        <v>45490</v>
+        <v>45504</v>
       </c>
       <c r="B19" t="s">
         <v>22</v>
       </c>
       <c r="C19" t="s">
-        <v>69</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
+      </c>
+      <c r="D19" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
-        <v>45482</v>
+        <v>45490</v>
       </c>
       <c r="B20" t="s">
         <v>22</v>
       </c>
       <c r="C20" t="s">
-        <v>67</v>
-      </c>
-      <c r="D20" t="s">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
-        <v>45473</v>
+        <v>45482</v>
       </c>
       <c r="B21" t="s">
         <v>22</v>
       </c>
       <c r="C21" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D21" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
-        <v>45443</v>
+        <v>45473</v>
       </c>
       <c r="B22" t="s">
         <v>22</v>
       </c>
       <c r="C22" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D22" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
-        <v>45357</v>
+        <v>45443</v>
       </c>
       <c r="B23" t="s">
         <v>22</v>
       </c>
       <c r="C23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D23" t="s">
-        <v>61</v>
-      </c>
-      <c r="E23" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
-        <v>45352</v>
+        <v>45357</v>
       </c>
       <c r="B24" t="s">
         <v>22</v>
       </c>
       <c r="C24" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D24" t="s">
-        <v>58</v>
+        <v>61</v>
+      </c>
+      <c r="E24" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
-        <v>45240</v>
+        <v>45352</v>
       </c>
       <c r="B25" t="s">
         <v>22</v>
       </c>
       <c r="C25" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D25" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
-        <v>45212</v>
+        <v>45240</v>
       </c>
       <c r="B26" t="s">
         <v>22</v>
       </c>
       <c r="C26" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D26" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
-        <v>45211</v>
-      </c>
-      <c r="B27" s="2" t="s">
+        <v>45212</v>
+      </c>
+      <c r="B27" t="s">
         <v>22</v>
       </c>
       <c r="C27" t="s">
-        <v>51</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
+      </c>
+      <c r="D27" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
-        <v>45147</v>
+        <v>45211</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C28" t="s">
-        <v>47</v>
-      </c>
-      <c r="D28" t="s">
-        <v>48</v>
-      </c>
-      <c r="E28" t="s">
-        <v>49</v>
+        <v>51</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
+        <v>45147</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29" t="s">
+        <v>47</v>
+      </c>
+      <c r="D29" t="s">
+        <v>48</v>
+      </c>
+      <c r="E29" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
         <v>45143</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C29" t="s">
+      <c r="B30" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C30" t="s">
         <v>44</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D30" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A30" s="2">
+    <row r="31" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A31" s="2">
         <v>45119</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C30" s="3" t="s">
+      <c r="B31" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D31" s="1" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="2">
-        <v>45113</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C31" t="s">
-        <v>26</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
-        <v>45112</v>
+        <v>45113</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C32" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
-        <v>45083</v>
+        <v>45112</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C33" t="s">
-        <v>12</v>
-      </c>
-      <c r="D33" t="s">
-        <v>3</v>
+        <v>28</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
-        <v>45082</v>
+        <v>45083</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C34" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D34" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
-        <v>45018</v>
+        <v>45082</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C35" t="s">
-        <v>54</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>55</v>
+        <v>13</v>
+      </c>
+      <c r="D35" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
-        <v>45014</v>
+        <v>45018</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C36" t="s">
-        <v>14</v>
-      </c>
-      <c r="D36" t="s">
-        <v>5</v>
+        <v>54</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
-        <v>44992</v>
+        <v>45014</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C37" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D37" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
-        <v>44959</v>
+        <v>44992</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C38" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D38" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
-        <v>44930</v>
+        <v>44959</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C39" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D39" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
-        <v>44897</v>
+        <v>44930</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C40" t="s">
-        <v>18</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
+      </c>
+      <c r="D40" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
-        <v>44682</v>
+        <v>44897</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C41" t="s">
-        <v>19</v>
-      </c>
-      <c r="D41" t="s">
-        <v>9</v>
+        <v>18</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
-        <v>44601</v>
+        <v>44682</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C42" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D42" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
-        <v>44725</v>
+        <v>44601</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C43" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D43" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
-        <v>44723</v>
+        <v>44725</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C44" t="s">
-        <v>42</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
+      </c>
+      <c r="D44" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
-        <v>44326</v>
+        <v>44723</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C45" t="s">
-        <v>38</v>
-      </c>
-      <c r="D45" t="s">
-        <v>39</v>
+        <v>42</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
-        <v>44265</v>
+        <v>44326</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C46" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D46" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
-        <v>44148</v>
+        <v>44265</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C47" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D47" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
-        <v>44146</v>
+        <v>44148</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C48" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D48" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
-        <v>44144</v>
+        <v>44146</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C49" t="s">
+        <v>32</v>
+      </c>
+      <c r="D49" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="2">
+        <v>44144</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C50" t="s">
         <v>31</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D50" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B50" s="2"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B51" s="2"/>
     </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B52" s="2"/>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A20:D40">
-    <sortCondition ref="B20:B40"/>
-    <sortCondition descending="1" ref="A20:A40"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A21:D41">
+    <sortCondition ref="B21:B41"/>
+    <sortCondition descending="1" ref="A21:A41"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="D40" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="D30" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="D31" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="D32" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="D44" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="D27" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="D35" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="D19" r:id="rId8" xr:uid="{FA3531C4-3B8B-4257-B20B-BB3BF511A818}"/>
-    <hyperlink ref="E12" r:id="rId9" xr:uid="{461EAE59-6B89-4B06-BC7F-5D62D70EDCD6}"/>
-    <hyperlink ref="D9" r:id="rId10" xr:uid="{9FC614FC-A94D-4784-8E8F-DFD619EA88C0}"/>
-    <hyperlink ref="D8" r:id="rId11" xr:uid="{0B29772C-F7FE-40CC-A257-2848F4518174}"/>
-    <hyperlink ref="E6" r:id="rId12" xr:uid="{C474B74F-3E03-433F-BC35-18768486A4FB}"/>
-    <hyperlink ref="E5" r:id="rId13" xr:uid="{209BE10C-36A4-4475-BDA6-365C34A7A7B4}"/>
-    <hyperlink ref="D4" r:id="rId14" xr:uid="{D908A389-6872-41E0-B81F-166FB55D55A3}"/>
-    <hyperlink ref="D3" r:id="rId15" xr:uid="{1BBDB9F5-EA33-4B8D-A13B-752105B1611A}"/>
+    <hyperlink ref="D41" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="D31" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="D32" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="D33" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="D45" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="D28" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="D36" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="D20" r:id="rId8" xr:uid="{FA3531C4-3B8B-4257-B20B-BB3BF511A818}"/>
+    <hyperlink ref="E13" r:id="rId9" xr:uid="{461EAE59-6B89-4B06-BC7F-5D62D70EDCD6}"/>
+    <hyperlink ref="D10" r:id="rId10" xr:uid="{9FC614FC-A94D-4784-8E8F-DFD619EA88C0}"/>
+    <hyperlink ref="D9" r:id="rId11" xr:uid="{0B29772C-F7FE-40CC-A257-2848F4518174}"/>
+    <hyperlink ref="E7" r:id="rId12" xr:uid="{C474B74F-3E03-433F-BC35-18768486A4FB}"/>
+    <hyperlink ref="E6" r:id="rId13" xr:uid="{209BE10C-36A4-4475-BDA6-365C34A7A7B4}"/>
+    <hyperlink ref="D5" r:id="rId14" xr:uid="{D908A389-6872-41E0-B81F-166FB55D55A3}"/>
+    <hyperlink ref="D4" r:id="rId15" xr:uid="{1BBDB9F5-EA33-4B8D-A13B-752105B1611A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId16"/>

--- a/data/posts.xlsx
+++ b/data/posts.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3E6C842-2D9D-43E2-97A0-27070F519647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48C04D85-1B1E-4A2E-8923-0C247C8E3D3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="111">
   <si>
     <t>date</t>
   </si>
@@ -358,6 +358,12 @@
   </si>
   <si>
     <t>https://www.linkedin.com/posts/kasparrufibach_in-virtually-all-clinical-trials-we-stratify-activity-7382149707659153408-lEbc?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAAQJ2qsB_r_XsYhAPWyf_WQeC5V6NOcbIXo</t>
+  </si>
+  <si>
+    <t>Nine questions about stratification and covariate adjustment: Part 2</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/posts/kasparrufibach_biostatistics-collaboration-randomization-activity-7388225051055063041-Hn0U?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAAQJ2qsB_r_XsYhAPWyf_WQeC5V6NOcbIXo</t>
   </si>
 </sst>
 </file>
@@ -700,7 +706,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -729,732 +735,746 @@
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
-        <v>45941</v>
+        <v>45956</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
-        <v>45927</v>
+        <v>45941</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
-        <v>45871</v>
+        <v>45927</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
+      </c>
+      <c r="D4" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
-        <v>45868</v>
+        <v>45871</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>45855</v>
+        <v>45868</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="D6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>84</v>
+      <c r="C6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <v>45784</v>
+        <v>45855</v>
       </c>
       <c r="B7" t="s">
         <v>22</v>
       </c>
-      <c r="C7" t="s">
-        <v>96</v>
+      <c r="C7" s="5" t="s">
+        <v>100</v>
       </c>
       <c r="D7" t="s">
-        <v>97</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>45725</v>
+        <v>45784</v>
       </c>
       <c r="B8" t="s">
         <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D8" t="s">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>45696</v>
+        <v>45725</v>
       </c>
       <c r="B9" t="s">
         <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
+      </c>
+      <c r="D9" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>45686</v>
+        <v>45696</v>
       </c>
       <c r="B10" t="s">
         <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
+        <v>45686</v>
+      </c>
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
         <v>45623</v>
       </c>
-      <c r="B11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" t="s">
         <v>89</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D12" t="s">
         <v>88</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
-        <v>45584</v>
-      </c>
-      <c r="B12" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D12" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
-        <v>45568</v>
+        <v>45584</v>
       </c>
       <c r="B13" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>85</v>
+      <c r="C13" t="s">
+        <v>87</v>
       </c>
       <c r="D13" t="s">
-        <v>83</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <v>45565</v>
+        <v>45568</v>
       </c>
       <c r="B14" t="s">
         <v>22</v>
       </c>
-      <c r="C14" t="s">
-        <v>82</v>
+      <c r="C14" s="5" t="s">
+        <v>85</v>
       </c>
       <c r="D14" t="s">
-        <v>81</v>
+        <v>83</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
-        <v>45557</v>
+        <v>45565</v>
       </c>
       <c r="B15" t="s">
         <v>22</v>
       </c>
       <c r="C15" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
-        <v>45537</v>
+        <v>45557</v>
       </c>
       <c r="B16" t="s">
         <v>22</v>
       </c>
       <c r="C16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D16" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
-        <v>45533</v>
+        <v>45537</v>
       </c>
       <c r="B17" t="s">
         <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D17" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
-        <v>45509</v>
+        <v>45533</v>
       </c>
       <c r="B18" t="s">
         <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D18" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
-        <v>45504</v>
+        <v>45509</v>
       </c>
       <c r="B19" t="s">
         <v>22</v>
       </c>
       <c r="C19" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D19" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
-        <v>45490</v>
+        <v>45504</v>
       </c>
       <c r="B20" t="s">
         <v>22</v>
       </c>
       <c r="C20" t="s">
-        <v>69</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
+      </c>
+      <c r="D20" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
-        <v>45482</v>
+        <v>45490</v>
       </c>
       <c r="B21" t="s">
         <v>22</v>
       </c>
       <c r="C21" t="s">
-        <v>67</v>
-      </c>
-      <c r="D21" t="s">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
-        <v>45473</v>
+        <v>45482</v>
       </c>
       <c r="B22" t="s">
         <v>22</v>
       </c>
       <c r="C22" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D22" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
-        <v>45443</v>
+        <v>45473</v>
       </c>
       <c r="B23" t="s">
         <v>22</v>
       </c>
       <c r="C23" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D23" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
-        <v>45357</v>
+        <v>45443</v>
       </c>
       <c r="B24" t="s">
         <v>22</v>
       </c>
       <c r="C24" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D24" t="s">
-        <v>61</v>
-      </c>
-      <c r="E24" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
-        <v>45352</v>
+        <v>45357</v>
       </c>
       <c r="B25" t="s">
         <v>22</v>
       </c>
       <c r="C25" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D25" t="s">
-        <v>58</v>
+        <v>61</v>
+      </c>
+      <c r="E25" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
-        <v>45240</v>
+        <v>45352</v>
       </c>
       <c r="B26" t="s">
         <v>22</v>
       </c>
       <c r="C26" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D26" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
-        <v>45212</v>
+        <v>45240</v>
       </c>
       <c r="B27" t="s">
         <v>22</v>
       </c>
       <c r="C27" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D27" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
-        <v>45211</v>
-      </c>
-      <c r="B28" s="2" t="s">
+        <v>45212</v>
+      </c>
+      <c r="B28" t="s">
         <v>22</v>
       </c>
       <c r="C28" t="s">
-        <v>51</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
+      </c>
+      <c r="D28" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
-        <v>45147</v>
+        <v>45211</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C29" t="s">
-        <v>47</v>
-      </c>
-      <c r="D29" t="s">
-        <v>48</v>
-      </c>
-      <c r="E29" t="s">
-        <v>49</v>
+        <v>51</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
+        <v>45147</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C30" t="s">
+        <v>47</v>
+      </c>
+      <c r="D30" t="s">
+        <v>48</v>
+      </c>
+      <c r="E30" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
         <v>45143</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C30" t="s">
+      <c r="B31" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C31" t="s">
         <v>44</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D31" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A31" s="2">
+    <row r="32" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A32" s="2">
         <v>45119</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C31" s="3" t="s">
+      <c r="B32" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D32" s="1" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="2">
-        <v>45113</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C32" t="s">
-        <v>26</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
-        <v>45112</v>
+        <v>45113</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C33" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
-        <v>45083</v>
+        <v>45112</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C34" t="s">
-        <v>12</v>
-      </c>
-      <c r="D34" t="s">
-        <v>3</v>
+        <v>28</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
-        <v>45082</v>
+        <v>45083</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C35" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D35" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
-        <v>45018</v>
+        <v>45082</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C36" t="s">
-        <v>54</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>55</v>
+        <v>13</v>
+      </c>
+      <c r="D36" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
-        <v>45014</v>
+        <v>45018</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C37" t="s">
-        <v>14</v>
-      </c>
-      <c r="D37" t="s">
-        <v>5</v>
+        <v>54</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
-        <v>44992</v>
+        <v>45014</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C38" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D38" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
-        <v>44959</v>
+        <v>44992</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C39" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D39" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
-        <v>44930</v>
+        <v>44959</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C40" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D40" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
-        <v>44897</v>
+        <v>44930</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C41" t="s">
-        <v>18</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
+      </c>
+      <c r="D41" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
-        <v>44682</v>
+        <v>44897</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C42" t="s">
-        <v>19</v>
-      </c>
-      <c r="D42" t="s">
-        <v>9</v>
+        <v>18</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
-        <v>44601</v>
+        <v>44682</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C43" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D43" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
-        <v>44725</v>
+        <v>44601</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C44" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D44" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
-        <v>44723</v>
+        <v>44725</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C45" t="s">
-        <v>42</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
+      </c>
+      <c r="D45" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
-        <v>44326</v>
+        <v>44723</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C46" t="s">
-        <v>38</v>
-      </c>
-      <c r="D46" t="s">
-        <v>39</v>
+        <v>42</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
-        <v>44265</v>
+        <v>44326</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C47" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D47" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
-        <v>44148</v>
+        <v>44265</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C48" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D48" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
-        <v>44146</v>
+        <v>44148</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C49" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D49" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
-        <v>44144</v>
+        <v>44146</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C50" t="s">
+        <v>32</v>
+      </c>
+      <c r="D50" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="2">
+        <v>44144</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C51" t="s">
         <v>31</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D51" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B51" s="2"/>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B52" s="2"/>
     </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B53" s="2"/>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A21:D41">
-    <sortCondition ref="B21:B41"/>
-    <sortCondition descending="1" ref="A21:A41"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A22:D42">
+    <sortCondition ref="B22:B42"/>
+    <sortCondition descending="1" ref="A22:A42"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="D41" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="D31" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="D32" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="D33" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="D45" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="D28" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="D36" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="D20" r:id="rId8" xr:uid="{FA3531C4-3B8B-4257-B20B-BB3BF511A818}"/>
-    <hyperlink ref="E13" r:id="rId9" xr:uid="{461EAE59-6B89-4B06-BC7F-5D62D70EDCD6}"/>
-    <hyperlink ref="D10" r:id="rId10" xr:uid="{9FC614FC-A94D-4784-8E8F-DFD619EA88C0}"/>
-    <hyperlink ref="D9" r:id="rId11" xr:uid="{0B29772C-F7FE-40CC-A257-2848F4518174}"/>
-    <hyperlink ref="E7" r:id="rId12" xr:uid="{C474B74F-3E03-433F-BC35-18768486A4FB}"/>
-    <hyperlink ref="E6" r:id="rId13" xr:uid="{209BE10C-36A4-4475-BDA6-365C34A7A7B4}"/>
-    <hyperlink ref="D5" r:id="rId14" xr:uid="{D908A389-6872-41E0-B81F-166FB55D55A3}"/>
-    <hyperlink ref="D4" r:id="rId15" xr:uid="{1BBDB9F5-EA33-4B8D-A13B-752105B1611A}"/>
+    <hyperlink ref="D42" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="D32" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="D33" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="D34" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="D46" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="D29" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="D37" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="D21" r:id="rId8" xr:uid="{FA3531C4-3B8B-4257-B20B-BB3BF511A818}"/>
+    <hyperlink ref="E14" r:id="rId9" xr:uid="{461EAE59-6B89-4B06-BC7F-5D62D70EDCD6}"/>
+    <hyperlink ref="D11" r:id="rId10" xr:uid="{9FC614FC-A94D-4784-8E8F-DFD619EA88C0}"/>
+    <hyperlink ref="D10" r:id="rId11" xr:uid="{0B29772C-F7FE-40CC-A257-2848F4518174}"/>
+    <hyperlink ref="E8" r:id="rId12" xr:uid="{C474B74F-3E03-433F-BC35-18768486A4FB}"/>
+    <hyperlink ref="E7" r:id="rId13" xr:uid="{209BE10C-36A4-4475-BDA6-365C34A7A7B4}"/>
+    <hyperlink ref="D6" r:id="rId14" xr:uid="{D908A389-6872-41E0-B81F-166FB55D55A3}"/>
+    <hyperlink ref="D5" r:id="rId15" xr:uid="{1BBDB9F5-EA33-4B8D-A13B-752105B1611A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId16"/>

--- a/data/posts.xlsx
+++ b/data/posts.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48C04D85-1B1E-4A2E-8923-0C247C8E3D3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9705760-B926-42D8-BE84-4F0425B5BD29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="115">
   <si>
     <t>date</t>
   </si>
@@ -364,6 +364,18 @@
   </si>
   <si>
     <t>https://www.linkedin.com/posts/kasparrufibach_biostatistics-collaboration-randomization-activity-7388225051055063041-Hn0U?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAAQJ2qsB_r_XsYhAPWyf_WQeC5V6NOcbIXo</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/posts/kasparrufibach_biostatistics-randomization-activity-7391225880049623040-L6px?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAAQJ2qsB_r_XsYhAPWyf_WQeC5V6NOcbIXo</t>
+  </si>
+  <si>
+    <t>Nine questions about stratification and covariate adjustment: Part 3</t>
+  </si>
+  <si>
+    <t>Marginal vs. conditional estimands</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/posts/kasparrufibach_biostatistics-activity-7391236766805942273-iIJj?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAAQJ2qsB_r_XsYhAPWyf_WQeC5V6NOcbIXo</t>
   </si>
 </sst>
 </file>
@@ -706,17 +718,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E53"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E55"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="106.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="106.7265625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="223" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="99.42578125" customWidth="1"/>
+    <col min="5" max="5" width="99.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -733,748 +745,776 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
+        <v>45964</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2">
+        <v>45964</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="2">
         <v>45956</v>
       </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
         <v>109</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D4" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
+    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="2">
         <v>45941</v>
       </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
         <v>107</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D5" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
+    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="2">
         <v>45927</v>
       </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
         <v>106</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D6" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
+    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2">
         <v>45871</v>
       </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
         <v>103</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
+    <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="2">
         <v>45868</v>
       </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
+    <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="2">
         <v>45855</v>
       </c>
-      <c r="B7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="5" t="s">
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D9" t="s">
         <v>99</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E9" s="4" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
+    <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="2">
         <v>45784</v>
       </c>
-      <c r="B8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" t="s">
         <v>96</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D10" t="s">
         <v>97</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
+    <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="2">
         <v>45725</v>
       </c>
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" t="s">
         <v>94</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D11" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
+    <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="2">
         <v>45696</v>
       </c>
-      <c r="B10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" t="s">
         <v>93</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D12" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
+    <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="2">
         <v>45686</v>
       </c>
-      <c r="B11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" t="s">
         <v>90</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
+    <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="2">
         <v>45623</v>
       </c>
-      <c r="B12" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="B14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" t="s">
         <v>89</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D14" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" s="2">
         <v>45584</v>
       </c>
-      <c r="B13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="B15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" t="s">
         <v>87</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D15" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" s="2">
         <v>45568</v>
       </c>
-      <c r="B14" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" s="5" t="s">
+      <c r="B16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D16" t="s">
         <v>83</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E16" s="4" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" s="2">
         <v>45565</v>
       </c>
-      <c r="B15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="B17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" t="s">
         <v>82</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D17" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="2">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" s="2">
         <v>45557</v>
       </c>
-      <c r="B16" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="B18" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" t="s">
         <v>79</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D18" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" s="2">
         <v>45537</v>
       </c>
-      <c r="B17" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="B19" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" t="s">
         <v>77</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D19" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" s="2">
         <v>45533</v>
       </c>
-      <c r="B18" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="B20" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" t="s">
         <v>75</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D20" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" s="2">
         <v>45509</v>
       </c>
-      <c r="B19" t="s">
-        <v>22</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="B21" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" t="s">
         <v>71</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D21" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" s="2">
         <v>45504</v>
       </c>
-      <c r="B20" t="s">
-        <v>22</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="B22" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" t="s">
         <v>73</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D22" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" s="2">
         <v>45490</v>
       </c>
-      <c r="B21" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="B23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" t="s">
         <v>69</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D23" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="2">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" s="2">
         <v>45482</v>
       </c>
-      <c r="B22" t="s">
-        <v>22</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="B24" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" t="s">
         <v>67</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D24" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" s="2">
         <v>45473</v>
       </c>
-      <c r="B23" t="s">
-        <v>22</v>
-      </c>
-      <c r="C23" t="s">
+      <c r="B25" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25" t="s">
         <v>65</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D25" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="2">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" s="2">
         <v>45443</v>
       </c>
-      <c r="B24" t="s">
-        <v>22</v>
-      </c>
-      <c r="C24" t="s">
+      <c r="B26" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" t="s">
         <v>63</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D26" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="2">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" s="2">
         <v>45357</v>
       </c>
-      <c r="B25" t="s">
-        <v>22</v>
-      </c>
-      <c r="C25" t="s">
+      <c r="B27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C27" t="s">
         <v>60</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D27" t="s">
         <v>61</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E27" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="2">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28" s="2">
         <v>45352</v>
       </c>
-      <c r="B26" t="s">
-        <v>22</v>
-      </c>
-      <c r="C26" t="s">
+      <c r="B28" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" t="s">
         <v>59</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D28" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="2">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" s="2">
         <v>45240</v>
       </c>
-      <c r="B27" t="s">
-        <v>22</v>
-      </c>
-      <c r="C27" t="s">
+      <c r="B29" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29" t="s">
         <v>57</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D29" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="2">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" s="2">
         <v>45212</v>
       </c>
-      <c r="B28" t="s">
-        <v>22</v>
-      </c>
-      <c r="C28" t="s">
+      <c r="B30" t="s">
+        <v>22</v>
+      </c>
+      <c r="C30" t="s">
         <v>53</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D30" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="2">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" s="2">
         <v>45211</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C29" t="s">
+      <c r="B31" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C31" t="s">
         <v>51</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D31" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="2">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32" s="2">
         <v>45147</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C30" t="s">
+      <c r="B32" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C32" t="s">
         <v>47</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D32" t="s">
         <v>48</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E32" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="2">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" s="2">
         <v>45143</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C31" t="s">
+      <c r="B33" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C33" t="s">
         <v>44</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D33" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A32" s="2">
+    <row r="34" spans="1:4" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A34" s="2">
         <v>45119</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C32" s="3" t="s">
+      <c r="B34" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D34" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="2">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" s="2">
         <v>45113</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C33" t="s">
+      <c r="B35" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C35" t="s">
         <v>26</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D35" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="2">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" s="2">
         <v>45112</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C34" t="s">
+      <c r="B36" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C36" t="s">
         <v>28</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D36" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="2">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" s="2">
         <v>45083</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C35" t="s">
+      <c r="B37" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C37" t="s">
         <v>12</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D37" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="2">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38" s="2">
         <v>45082</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C36" t="s">
+      <c r="B38" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C38" t="s">
         <v>13</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D38" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="2">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39" s="2">
         <v>45018</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C37" t="s">
+      <c r="B39" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C39" t="s">
         <v>54</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D39" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="2">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40" s="2">
         <v>45014</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C38" t="s">
+      <c r="B40" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C40" t="s">
         <v>14</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D40" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="2">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41" s="2">
         <v>44992</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C39" t="s">
+      <c r="B41" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" t="s">
         <v>15</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D41" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="2">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42" s="2">
         <v>44959</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C40" t="s">
+      <c r="B42" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C42" t="s">
         <v>16</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D42" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="2">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43" s="2">
         <v>44930</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C41" t="s">
+      <c r="B43" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C43" t="s">
         <v>17</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D43" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="2">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" s="2">
         <v>44897</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C42" t="s">
+      <c r="B44" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C44" t="s">
         <v>18</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="D44" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="2">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45" s="2">
         <v>44682</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C43" t="s">
+      <c r="B45" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C45" t="s">
         <v>19</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D45" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="2">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46" s="2">
         <v>44601</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C44" t="s">
+      <c r="B46" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C46" t="s">
         <v>20</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D46" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="2">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47" s="2">
         <v>44725</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C45" t="s">
-        <v>40</v>
-      </c>
-      <c r="D45" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="2">
-        <v>44723</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C46" t="s">
-        <v>42</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="2">
-        <v>44326</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C47" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D47" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
-        <v>44265</v>
+        <v>44723</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C48" t="s">
-        <v>36</v>
-      </c>
-      <c r="D48" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
-        <v>44148</v>
+        <v>44326</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C49" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D49" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
-        <v>44146</v>
+        <v>44265</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C50" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D50" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
-        <v>44144</v>
+        <v>44148</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C51" t="s">
+        <v>34</v>
+      </c>
+      <c r="D51" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52" s="2">
+        <v>44146</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C52" t="s">
+        <v>32</v>
+      </c>
+      <c r="D52" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53" s="2">
+        <v>44144</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C53" t="s">
         <v>31</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D53" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B52" s="2"/>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B53" s="2"/>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B54" s="2"/>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B55" s="2"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A22:D42">
-    <sortCondition ref="B22:B42"/>
-    <sortCondition descending="1" ref="A22:A42"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A24:D44">
+    <sortCondition ref="B24:B44"/>
+    <sortCondition descending="1" ref="A24:A44"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="D42" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="D32" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="D33" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="D34" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="D46" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="D29" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="D37" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="D21" r:id="rId8" xr:uid="{FA3531C4-3B8B-4257-B20B-BB3BF511A818}"/>
-    <hyperlink ref="E14" r:id="rId9" xr:uid="{461EAE59-6B89-4B06-BC7F-5D62D70EDCD6}"/>
-    <hyperlink ref="D11" r:id="rId10" xr:uid="{9FC614FC-A94D-4784-8E8F-DFD619EA88C0}"/>
-    <hyperlink ref="D10" r:id="rId11" xr:uid="{0B29772C-F7FE-40CC-A257-2848F4518174}"/>
-    <hyperlink ref="E8" r:id="rId12" xr:uid="{C474B74F-3E03-433F-BC35-18768486A4FB}"/>
-    <hyperlink ref="E7" r:id="rId13" xr:uid="{209BE10C-36A4-4475-BDA6-365C34A7A7B4}"/>
-    <hyperlink ref="D6" r:id="rId14" xr:uid="{D908A389-6872-41E0-B81F-166FB55D55A3}"/>
-    <hyperlink ref="D5" r:id="rId15" xr:uid="{1BBDB9F5-EA33-4B8D-A13B-752105B1611A}"/>
+    <hyperlink ref="D44" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="D34" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="D35" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="D36" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="D48" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="D31" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="D39" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="D23" r:id="rId8" xr:uid="{FA3531C4-3B8B-4257-B20B-BB3BF511A818}"/>
+    <hyperlink ref="E16" r:id="rId9" xr:uid="{461EAE59-6B89-4B06-BC7F-5D62D70EDCD6}"/>
+    <hyperlink ref="D13" r:id="rId10" xr:uid="{9FC614FC-A94D-4784-8E8F-DFD619EA88C0}"/>
+    <hyperlink ref="D12" r:id="rId11" xr:uid="{0B29772C-F7FE-40CC-A257-2848F4518174}"/>
+    <hyperlink ref="E10" r:id="rId12" xr:uid="{C474B74F-3E03-433F-BC35-18768486A4FB}"/>
+    <hyperlink ref="E9" r:id="rId13" xr:uid="{209BE10C-36A4-4475-BDA6-365C34A7A7B4}"/>
+    <hyperlink ref="D8" r:id="rId14" xr:uid="{D908A389-6872-41E0-B81F-166FB55D55A3}"/>
+    <hyperlink ref="D7" r:id="rId15" xr:uid="{1BBDB9F5-EA33-4B8D-A13B-752105B1611A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId16"/>

--- a/data/posts.xlsx
+++ b/data/posts.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9705760-B926-42D8-BE84-4F0425B5BD29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D9C09D0-C9B9-4500-ADF4-3325BD399FD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="117">
   <si>
     <t>date</t>
   </si>
@@ -376,6 +376,12 @@
   </si>
   <si>
     <t>https://www.linkedin.com/posts/kasparrufibach_biostatistics-activity-7391236766805942273-iIJj?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAAQJ2qsB_r_XsYhAPWyf_WQeC5V6NOcbIXo</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/posts/kasparrufibach_specifying-a-target-trial-prevents-immortal-activity-7388872606973665281-vIvO?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAAQJ2qsB_r_XsYhAPWyf_WQeC5V6NOcbIXo</t>
+  </si>
+  <si>
+    <t>Nature paper on covid vaccines amplifying effect of immunotherapy: immortal bias!</t>
   </si>
 </sst>
 </file>
@@ -718,17 +724,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E55"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:E56"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="106.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="106.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="223" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="99.453125" customWidth="1"/>
+    <col min="5" max="5" width="99.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -745,7 +751,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>45964</v>
       </c>
@@ -759,7 +765,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>45964</v>
       </c>
@@ -773,748 +779,762 @@
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
+        <v>45959</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
         <v>45956</v>
       </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
         <v>109</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D5" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="2">
+    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
         <v>45941</v>
       </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
         <v>107</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D6" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="2">
+    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
         <v>45927</v>
       </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
         <v>106</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D7" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="2">
+    <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
         <v>45871</v>
       </c>
-      <c r="B7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
         <v>103</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="2">
+    <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
         <v>45868</v>
       </c>
-      <c r="B8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
         <v>102</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="2">
+    <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
         <v>45855</v>
       </c>
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="5" t="s">
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D10" t="s">
         <v>99</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E10" s="4" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="2">
+    <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
         <v>45784</v>
       </c>
-      <c r="B10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" t="s">
         <v>96</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D11" t="s">
         <v>97</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E11" s="1" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="2">
+    <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
         <v>45725</v>
       </c>
-      <c r="B11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" t="s">
         <v>94</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D12" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="2">
+    <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
         <v>45696</v>
       </c>
-      <c r="B12" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" t="s">
         <v>93</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="2">
+    <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
         <v>45686</v>
       </c>
-      <c r="B13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="B14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" t="s">
         <v>90</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="2">
+    <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
         <v>45623</v>
       </c>
-      <c r="B14" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="B15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" t="s">
         <v>89</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D15" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
         <v>45584</v>
       </c>
-      <c r="B15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="B16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" t="s">
         <v>87</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D16" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
         <v>45568</v>
       </c>
-      <c r="B16" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" s="5" t="s">
+      <c r="B17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D17" t="s">
         <v>83</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E17" s="4" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="2">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
         <v>45565</v>
       </c>
-      <c r="B17" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="B18" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" t="s">
         <v>82</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D18" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" s="2">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
         <v>45557</v>
       </c>
-      <c r="B18" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="B19" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" t="s">
         <v>79</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D19" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" s="2">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
         <v>45537</v>
       </c>
-      <c r="B19" t="s">
-        <v>22</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="B20" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" t="s">
         <v>77</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D20" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" s="2">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
         <v>45533</v>
       </c>
-      <c r="B20" t="s">
-        <v>22</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="B21" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" t="s">
         <v>75</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D21" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" s="2">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
         <v>45509</v>
       </c>
-      <c r="B21" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="B22" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" t="s">
         <v>71</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D22" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A22" s="2">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
         <v>45504</v>
       </c>
-      <c r="B22" t="s">
-        <v>22</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="B23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" t="s">
         <v>73</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D23" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A23" s="2">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
         <v>45490</v>
       </c>
-      <c r="B23" t="s">
-        <v>22</v>
-      </c>
-      <c r="C23" t="s">
+      <c r="B24" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" t="s">
         <v>69</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D24" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A24" s="2">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
         <v>45482</v>
       </c>
-      <c r="B24" t="s">
-        <v>22</v>
-      </c>
-      <c r="C24" t="s">
+      <c r="B25" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25" t="s">
         <v>67</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D25" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A25" s="2">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
         <v>45473</v>
       </c>
-      <c r="B25" t="s">
-        <v>22</v>
-      </c>
-      <c r="C25" t="s">
+      <c r="B26" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" t="s">
         <v>65</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D26" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A26" s="2">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
         <v>45443</v>
       </c>
-      <c r="B26" t="s">
-        <v>22</v>
-      </c>
-      <c r="C26" t="s">
+      <c r="B27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C27" t="s">
         <v>63</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D27" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A27" s="2">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
         <v>45357</v>
       </c>
-      <c r="B27" t="s">
-        <v>22</v>
-      </c>
-      <c r="C27" t="s">
+      <c r="B28" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" t="s">
         <v>60</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D28" t="s">
         <v>61</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E28" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A28" s="2">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
         <v>45352</v>
       </c>
-      <c r="B28" t="s">
-        <v>22</v>
-      </c>
-      <c r="C28" t="s">
+      <c r="B29" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29" t="s">
         <v>59</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D29" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A29" s="2">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
         <v>45240</v>
       </c>
-      <c r="B29" t="s">
-        <v>22</v>
-      </c>
-      <c r="C29" t="s">
+      <c r="B30" t="s">
+        <v>22</v>
+      </c>
+      <c r="C30" t="s">
         <v>57</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D30" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A30" s="2">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
         <v>45212</v>
       </c>
-      <c r="B30" t="s">
-        <v>22</v>
-      </c>
-      <c r="C30" t="s">
+      <c r="B31" t="s">
+        <v>22</v>
+      </c>
+      <c r="C31" t="s">
         <v>53</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D31" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A31" s="2">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
         <v>45211</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C31" t="s">
+      <c r="B32" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C32" t="s">
         <v>51</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D32" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A32" s="2">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
         <v>45147</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C32" t="s">
+      <c r="B33" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C33" t="s">
         <v>47</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D33" t="s">
         <v>48</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E33" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" s="2">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
         <v>45143</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C33" t="s">
+      <c r="B34" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C34" t="s">
         <v>44</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D34" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A34" s="2">
+    <row r="35" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A35" s="2">
         <v>45119</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C34" s="3" t="s">
+      <c r="B35" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D35" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" s="2">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
         <v>45113</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C35" t="s">
+      <c r="B36" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C36" t="s">
         <v>26</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="D36" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" s="2">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
         <v>45112</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C36" t="s">
+      <c r="B37" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C37" t="s">
         <v>28</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D37" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" s="2">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
         <v>45083</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C37" t="s">
+      <c r="B38" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C38" t="s">
         <v>12</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D38" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" s="2">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="2">
         <v>45082</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C38" t="s">
+      <c r="B39" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C39" t="s">
         <v>13</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D39" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" s="2">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
         <v>45018</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C39" t="s">
+      <c r="B40" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C40" t="s">
         <v>54</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="D40" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" s="2">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="2">
         <v>45014</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C40" t="s">
+      <c r="B41" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" t="s">
         <v>14</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D41" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" s="2">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
         <v>44992</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C41" t="s">
+      <c r="B42" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C42" t="s">
         <v>15</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D42" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" s="2">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="2">
         <v>44959</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C42" t="s">
+      <c r="B43" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C43" t="s">
         <v>16</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D43" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" s="2">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
         <v>44930</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C43" t="s">
+      <c r="B44" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C44" t="s">
         <v>17</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D44" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" s="2">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="2">
         <v>44897</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C44" t="s">
+      <c r="B45" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C45" t="s">
         <v>18</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="D45" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" s="2">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="2">
         <v>44682</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C45" t="s">
+      <c r="B46" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C46" t="s">
         <v>19</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D46" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" s="2">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="2">
         <v>44601</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C46" t="s">
+      <c r="B47" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C47" t="s">
         <v>20</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D47" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" s="2">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="2">
         <v>44725</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C47" t="s">
-        <v>40</v>
-      </c>
-      <c r="D47" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48" s="2">
-        <v>44723</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C48" t="s">
-        <v>42</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+        <v>40</v>
+      </c>
+      <c r="D48" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
-        <v>44326</v>
+        <v>44723</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C49" t="s">
-        <v>38</v>
-      </c>
-      <c r="D49" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+        <v>42</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
-        <v>44265</v>
+        <v>44326</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C50" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D50" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
-        <v>44148</v>
+        <v>44265</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C51" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D51" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
-        <v>44146</v>
+        <v>44148</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C52" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D52" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
-        <v>44144</v>
+        <v>44146</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C53" t="s">
+        <v>32</v>
+      </c>
+      <c r="D53" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="2">
+        <v>44144</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C54" t="s">
         <v>31</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D54" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B54" s="2"/>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B55" s="2"/>
     </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B56" s="2"/>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A24:D44">
-    <sortCondition ref="B24:B44"/>
-    <sortCondition descending="1" ref="A24:A44"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A25:D45">
+    <sortCondition ref="B25:B45"/>
+    <sortCondition descending="1" ref="A25:A45"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="D44" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="D34" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="D35" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="D36" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="D48" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="D31" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="D39" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="D23" r:id="rId8" xr:uid="{FA3531C4-3B8B-4257-B20B-BB3BF511A818}"/>
-    <hyperlink ref="E16" r:id="rId9" xr:uid="{461EAE59-6B89-4B06-BC7F-5D62D70EDCD6}"/>
-    <hyperlink ref="D13" r:id="rId10" xr:uid="{9FC614FC-A94D-4784-8E8F-DFD619EA88C0}"/>
-    <hyperlink ref="D12" r:id="rId11" xr:uid="{0B29772C-F7FE-40CC-A257-2848F4518174}"/>
-    <hyperlink ref="E10" r:id="rId12" xr:uid="{C474B74F-3E03-433F-BC35-18768486A4FB}"/>
-    <hyperlink ref="E9" r:id="rId13" xr:uid="{209BE10C-36A4-4475-BDA6-365C34A7A7B4}"/>
-    <hyperlink ref="D8" r:id="rId14" xr:uid="{D908A389-6872-41E0-B81F-166FB55D55A3}"/>
-    <hyperlink ref="D7" r:id="rId15" xr:uid="{1BBDB9F5-EA33-4B8D-A13B-752105B1611A}"/>
+    <hyperlink ref="D45" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="D35" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="D36" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="D37" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="D49" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="D32" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="D40" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="D24" r:id="rId8" xr:uid="{FA3531C4-3B8B-4257-B20B-BB3BF511A818}"/>
+    <hyperlink ref="E17" r:id="rId9" xr:uid="{461EAE59-6B89-4B06-BC7F-5D62D70EDCD6}"/>
+    <hyperlink ref="D14" r:id="rId10" xr:uid="{9FC614FC-A94D-4784-8E8F-DFD619EA88C0}"/>
+    <hyperlink ref="D13" r:id="rId11" xr:uid="{0B29772C-F7FE-40CC-A257-2848F4518174}"/>
+    <hyperlink ref="E11" r:id="rId12" xr:uid="{C474B74F-3E03-433F-BC35-18768486A4FB}"/>
+    <hyperlink ref="E10" r:id="rId13" xr:uid="{209BE10C-36A4-4475-BDA6-365C34A7A7B4}"/>
+    <hyperlink ref="D9" r:id="rId14" xr:uid="{D908A389-6872-41E0-B81F-166FB55D55A3}"/>
+    <hyperlink ref="D8" r:id="rId15" xr:uid="{1BBDB9F5-EA33-4B8D-A13B-752105B1611A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId16"/>

--- a/data/posts.xlsx
+++ b/data/posts.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D9C09D0-C9B9-4500-ADF4-3325BD399FD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D3ED194-8768-4218-8E67-B4580BFE573D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="120">
   <si>
     <t>date</t>
   </si>
@@ -382,6 +382,15 @@
   </si>
   <si>
     <t>Nature paper on covid vaccines amplifying effect of immunotherapy: immortal bias!</t>
+  </si>
+  <si>
+    <t>Do you have precedence?</t>
+  </si>
+  <si>
+    <t>Three podcast episodes and ICH E20 expert writing group</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/posts/kasparrufibach_innovation-biostatistics-drugdevelopment-activity-7400184689887453184-gfFv?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAAQJ2qsB_r_XsYhAPWyf_WQeC5V6NOcbIXo</t>
   </si>
 </sst>
 </file>
@@ -724,17 +733,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E56"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E58"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="106.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="106.7265625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="223" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="99.42578125" customWidth="1"/>
+    <col min="5" max="5" width="99.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -751,790 +760,818 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
+        <v>45992</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2">
+        <v>45989</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="2">
         <v>45964</v>
       </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
         <v>113</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D4" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
+    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="2">
         <v>45964</v>
       </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
         <v>112</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D5" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
+    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="2">
         <v>45959</v>
       </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
         <v>116</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D6" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
+    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2">
         <v>45956</v>
       </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
         <v>109</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D7" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
+    <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="2">
         <v>45941</v>
       </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
         <v>107</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D8" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
+    <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="2">
         <v>45927</v>
       </c>
-      <c r="B7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
         <v>106</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D9" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
+    <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="2">
         <v>45871</v>
       </c>
-      <c r="B8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" t="s">
         <v>103</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
+    <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="2">
         <v>45868</v>
       </c>
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" t="s">
         <v>102</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
+    <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="2">
         <v>45855</v>
       </c>
-      <c r="B10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="5" t="s">
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D12" t="s">
         <v>99</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E12" s="4" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
+    <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="2">
         <v>45784</v>
       </c>
-      <c r="B11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" t="s">
         <v>96</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D13" t="s">
         <v>97</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E13" s="1" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
+    <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="2">
         <v>45725</v>
       </c>
-      <c r="B12" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="B14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" t="s">
         <v>94</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D14" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
+    <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="2">
         <v>45696</v>
       </c>
-      <c r="B13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="B15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" t="s">
         <v>93</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D15" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
+    <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="2">
         <v>45686</v>
       </c>
-      <c r="B14" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="B16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" t="s">
         <v>90</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D16" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
+    <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="2">
         <v>45623</v>
       </c>
-      <c r="B15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="B17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" t="s">
         <v>89</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D17" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="2">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" s="2">
         <v>45584</v>
       </c>
-      <c r="B16" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="B18" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" t="s">
         <v>87</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D18" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" s="2">
         <v>45568</v>
       </c>
-      <c r="B17" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" s="5" t="s">
+      <c r="B19" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D19" t="s">
         <v>83</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E19" s="4" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" s="2">
         <v>45565</v>
       </c>
-      <c r="B18" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="B20" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" t="s">
         <v>82</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D20" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" s="2">
         <v>45557</v>
       </c>
-      <c r="B19" t="s">
-        <v>22</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="B21" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" t="s">
         <v>79</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D21" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" s="2">
         <v>45537</v>
       </c>
-      <c r="B20" t="s">
-        <v>22</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="B22" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" t="s">
         <v>77</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D22" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" s="2">
         <v>45533</v>
       </c>
-      <c r="B21" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="B23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" t="s">
         <v>75</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D23" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="2">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" s="2">
         <v>45509</v>
       </c>
-      <c r="B22" t="s">
-        <v>22</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="B24" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" t="s">
         <v>71</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D24" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" s="2">
         <v>45504</v>
       </c>
-      <c r="B23" t="s">
-        <v>22</v>
-      </c>
-      <c r="C23" t="s">
+      <c r="B25" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25" t="s">
         <v>73</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D25" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="2">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" s="2">
         <v>45490</v>
       </c>
-      <c r="B24" t="s">
-        <v>22</v>
-      </c>
-      <c r="C24" t="s">
+      <c r="B26" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" t="s">
         <v>69</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D26" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="2">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" s="2">
         <v>45482</v>
       </c>
-      <c r="B25" t="s">
-        <v>22</v>
-      </c>
-      <c r="C25" t="s">
+      <c r="B27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C27" t="s">
         <v>67</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D27" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="2">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28" s="2">
         <v>45473</v>
       </c>
-      <c r="B26" t="s">
-        <v>22</v>
-      </c>
-      <c r="C26" t="s">
+      <c r="B28" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" t="s">
         <v>65</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D28" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="2">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" s="2">
         <v>45443</v>
       </c>
-      <c r="B27" t="s">
-        <v>22</v>
-      </c>
-      <c r="C27" t="s">
+      <c r="B29" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29" t="s">
         <v>63</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D29" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="2">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" s="2">
         <v>45357</v>
       </c>
-      <c r="B28" t="s">
-        <v>22</v>
-      </c>
-      <c r="C28" t="s">
+      <c r="B30" t="s">
+        <v>22</v>
+      </c>
+      <c r="C30" t="s">
         <v>60</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D30" t="s">
         <v>61</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E30" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="2">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" s="2">
         <v>45352</v>
       </c>
-      <c r="B29" t="s">
-        <v>22</v>
-      </c>
-      <c r="C29" t="s">
+      <c r="B31" t="s">
+        <v>22</v>
+      </c>
+      <c r="C31" t="s">
         <v>59</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D31" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="2">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32" s="2">
         <v>45240</v>
       </c>
-      <c r="B30" t="s">
-        <v>22</v>
-      </c>
-      <c r="C30" t="s">
+      <c r="B32" t="s">
+        <v>22</v>
+      </c>
+      <c r="C32" t="s">
         <v>57</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D32" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="2">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A33" s="2">
         <v>45212</v>
       </c>
-      <c r="B31" t="s">
-        <v>22</v>
-      </c>
-      <c r="C31" t="s">
+      <c r="B33" t="s">
+        <v>22</v>
+      </c>
+      <c r="C33" t="s">
         <v>53</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D33" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="2">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A34" s="2">
         <v>45211</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C32" t="s">
+      <c r="B34" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C34" t="s">
         <v>51</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D34" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="2">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A35" s="2">
         <v>45147</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C33" t="s">
+      <c r="B35" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C35" t="s">
         <v>47</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D35" t="s">
         <v>48</v>
       </c>
-      <c r="E33" t="s">
+      <c r="E35" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="2">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A36" s="2">
         <v>45143</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C34" t="s">
+      <c r="B36" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C36" t="s">
         <v>44</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D36" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A35" s="2">
+    <row r="37" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A37" s="2">
         <v>45119</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C35" s="3" t="s">
+      <c r="B37" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="D37" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="2">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A38" s="2">
         <v>45113</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C36" t="s">
+      <c r="B38" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C38" t="s">
         <v>26</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D38" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="2">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A39" s="2">
         <v>45112</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C37" t="s">
+      <c r="B39" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C39" t="s">
         <v>28</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D39" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="2">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A40" s="2">
         <v>45083</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C38" t="s">
+      <c r="B40" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C40" t="s">
         <v>12</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D40" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="2">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A41" s="2">
         <v>45082</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C39" t="s">
+      <c r="B41" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" t="s">
         <v>13</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D41" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="2">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A42" s="2">
         <v>45018</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C40" t="s">
+      <c r="B42" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C42" t="s">
         <v>54</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="D42" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="2">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A43" s="2">
         <v>45014</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C41" t="s">
+      <c r="B43" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C43" t="s">
         <v>14</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D43" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="2">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A44" s="2">
         <v>44992</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C42" t="s">
+      <c r="B44" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C44" t="s">
         <v>15</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D44" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="2">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A45" s="2">
         <v>44959</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C43" t="s">
+      <c r="B45" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C45" t="s">
         <v>16</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D45" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="2">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A46" s="2">
         <v>44930</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C44" t="s">
+      <c r="B46" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C46" t="s">
         <v>17</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D46" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="2">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A47" s="2">
         <v>44897</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C45" t="s">
+      <c r="B47" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C47" t="s">
         <v>18</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="D47" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="2">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A48" s="2">
         <v>44682</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C46" t="s">
+      <c r="B48" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C48" t="s">
         <v>19</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D48" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="2">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49" s="2">
         <v>44601</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C47" t="s">
+      <c r="B49" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C49" t="s">
         <v>20</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D49" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="2">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50" s="2">
         <v>44725</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C48" t="s">
-        <v>40</v>
-      </c>
-      <c r="D48" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="2">
-        <v>44723</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C49" t="s">
-        <v>42</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="2">
-        <v>44326</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C50" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D50" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
-        <v>44265</v>
+        <v>44723</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C51" t="s">
-        <v>36</v>
-      </c>
-      <c r="D51" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
-        <v>44148</v>
+        <v>44326</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C52" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D52" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" s="2">
-        <v>44146</v>
+        <v>44265</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C53" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D53" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
-        <v>44144</v>
+        <v>44148</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C54" t="s">
+        <v>34</v>
+      </c>
+      <c r="D54" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55" s="2">
+        <v>44146</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C55" t="s">
+        <v>32</v>
+      </c>
+      <c r="D55" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56" s="2">
+        <v>44144</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C56" t="s">
         <v>31</v>
       </c>
-      <c r="D54" t="s">
+      <c r="D56" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B55" s="2"/>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B56" s="2"/>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B57" s="2"/>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B58" s="2"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A25:D45">
-    <sortCondition ref="B25:B45"/>
-    <sortCondition descending="1" ref="A25:A45"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A27:D47">
+    <sortCondition ref="B27:B47"/>
+    <sortCondition descending="1" ref="A27:A47"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="D45" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="D35" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="D36" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="D37" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="D49" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="D32" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="D40" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="D24" r:id="rId8" xr:uid="{FA3531C4-3B8B-4257-B20B-BB3BF511A818}"/>
-    <hyperlink ref="E17" r:id="rId9" xr:uid="{461EAE59-6B89-4B06-BC7F-5D62D70EDCD6}"/>
-    <hyperlink ref="D14" r:id="rId10" xr:uid="{9FC614FC-A94D-4784-8E8F-DFD619EA88C0}"/>
-    <hyperlink ref="D13" r:id="rId11" xr:uid="{0B29772C-F7FE-40CC-A257-2848F4518174}"/>
-    <hyperlink ref="E11" r:id="rId12" xr:uid="{C474B74F-3E03-433F-BC35-18768486A4FB}"/>
-    <hyperlink ref="E10" r:id="rId13" xr:uid="{209BE10C-36A4-4475-BDA6-365C34A7A7B4}"/>
-    <hyperlink ref="D9" r:id="rId14" xr:uid="{D908A389-6872-41E0-B81F-166FB55D55A3}"/>
-    <hyperlink ref="D8" r:id="rId15" xr:uid="{1BBDB9F5-EA33-4B8D-A13B-752105B1611A}"/>
+    <hyperlink ref="D47" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="D37" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="D38" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="D39" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="D51" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="D34" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="D42" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="D26" r:id="rId8" xr:uid="{FA3531C4-3B8B-4257-B20B-BB3BF511A818}"/>
+    <hyperlink ref="E19" r:id="rId9" xr:uid="{461EAE59-6B89-4B06-BC7F-5D62D70EDCD6}"/>
+    <hyperlink ref="D16" r:id="rId10" xr:uid="{9FC614FC-A94D-4784-8E8F-DFD619EA88C0}"/>
+    <hyperlink ref="D15" r:id="rId11" xr:uid="{0B29772C-F7FE-40CC-A257-2848F4518174}"/>
+    <hyperlink ref="E13" r:id="rId12" xr:uid="{C474B74F-3E03-433F-BC35-18768486A4FB}"/>
+    <hyperlink ref="E12" r:id="rId13" xr:uid="{209BE10C-36A4-4475-BDA6-365C34A7A7B4}"/>
+    <hyperlink ref="D11" r:id="rId14" xr:uid="{D908A389-6872-41E0-B81F-166FB55D55A3}"/>
+    <hyperlink ref="D10" r:id="rId15" xr:uid="{1BBDB9F5-EA33-4B8D-A13B-752105B1611A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId16"/>

--- a/data/posts.xlsx
+++ b/data/posts.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D3ED194-8768-4218-8E67-B4580BFE573D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FD44AEB-1B09-493C-BE67-F135A3FD781A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="121">
   <si>
     <t>date</t>
   </si>
@@ -391,6 +391,9 @@
   </si>
   <si>
     <t>https://www.linkedin.com/posts/kasparrufibach_innovation-biostatistics-drugdevelopment-activity-7400184689887453184-gfFv?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAAQJ2qsB_r_XsYhAPWyf_WQeC5V6NOcbIXo</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/posts/kasparrufibach_biostatistics-drugdevelopment-activity-7401249156087832576-1kp0?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAAQJ2qsB_r_XsYhAPWyf_WQeC5V6NOcbIXo</t>
   </si>
 </sst>
 </file>
@@ -771,7 +774,7 @@
         <v>118</v>
       </c>
       <c r="D2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">

--- a/data/posts.xlsx
+++ b/data/posts.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FD44AEB-1B09-493C-BE67-F135A3FD781A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0F9AFD2-D95A-42D2-976E-EE0AE1D2436A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4940" yWindow="4940" windowWidth="28800" windowHeight="15450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="123">
   <si>
     <t>date</t>
   </si>
@@ -394,6 +394,12 @@
   </si>
   <si>
     <t>https://www.linkedin.com/posts/kasparrufibach_biostatistics-drugdevelopment-activity-7401249156087832576-1kp0?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAAQJ2qsB_r_XsYhAPWyf_WQeC5V6NOcbIXo</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/posts/kasparrufibach_biostatistics-illnessdeathmodel-oncology-activity-7404519700908482560-7cFJ?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAAQJ2qsB_r_XsYhAPWyf_WQeC5V6NOcbIXo</t>
+  </si>
+  <si>
+    <t>Theoretical joint distribution of logrank test for PFS and OS</t>
   </si>
 </sst>
 </file>
@@ -736,7 +742,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.1796875" bestFit="1" customWidth="1"/>
@@ -765,44 +771,44 @@
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
-        <v>45992</v>
+        <v>46001</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>117</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
+      </c>
+      <c r="D3" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
-        <v>45964</v>
+        <v>45989</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>113</v>
-      </c>
-      <c r="D4" t="s">
-        <v>114</v>
+        <v>117</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -813,768 +819,782 @@
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
-        <v>45959</v>
+        <v>45964</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D6" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
-        <v>45956</v>
+        <v>45959</v>
       </c>
       <c r="B7" t="s">
         <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D7" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
-        <v>45941</v>
+        <v>45956</v>
       </c>
       <c r="B8" t="s">
         <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D8" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
-        <v>45927</v>
+        <v>45941</v>
       </c>
       <c r="B9" t="s">
         <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D9" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
-        <v>45871</v>
+        <v>45927</v>
       </c>
       <c r="B10" t="s">
         <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>103</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
+      </c>
+      <c r="D10" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
-        <v>45868</v>
+        <v>45871</v>
       </c>
       <c r="B11" t="s">
         <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
-        <v>45855</v>
+        <v>45868</v>
       </c>
       <c r="B12" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="D12" t="s">
-        <v>99</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>84</v>
+      <c r="C12" t="s">
+        <v>102</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
-        <v>45784</v>
+        <v>45855</v>
       </c>
       <c r="B13" t="s">
         <v>22</v>
       </c>
-      <c r="C13" t="s">
-        <v>96</v>
+      <c r="C13" s="5" t="s">
+        <v>100</v>
       </c>
       <c r="D13" t="s">
-        <v>97</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
-        <v>45725</v>
+        <v>45784</v>
       </c>
       <c r="B14" t="s">
         <v>22</v>
       </c>
       <c r="C14" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D14" t="s">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
-        <v>45696</v>
+        <v>45725</v>
       </c>
       <c r="B15" t="s">
         <v>22</v>
       </c>
       <c r="C15" t="s">
-        <v>93</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
+      </c>
+      <c r="D15" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
-        <v>45686</v>
+        <v>45696</v>
       </c>
       <c r="B16" t="s">
         <v>22</v>
       </c>
       <c r="C16" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
+        <v>45686</v>
+      </c>
+      <c r="B17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" t="s">
+        <v>90</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="2">
         <v>45623</v>
       </c>
-      <c r="B17" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="B18" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" t="s">
         <v>89</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D18" t="s">
         <v>88</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" s="2">
-        <v>45584</v>
-      </c>
-      <c r="B18" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" t="s">
-        <v>87</v>
-      </c>
-      <c r="D18" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
-        <v>45568</v>
+        <v>45584</v>
       </c>
       <c r="B19" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="5" t="s">
-        <v>85</v>
+      <c r="C19" t="s">
+        <v>87</v>
       </c>
       <c r="D19" t="s">
-        <v>83</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
-        <v>45565</v>
+        <v>45568</v>
       </c>
       <c r="B20" t="s">
         <v>22</v>
       </c>
-      <c r="C20" t="s">
-        <v>82</v>
+      <c r="C20" s="5" t="s">
+        <v>85</v>
       </c>
       <c r="D20" t="s">
-        <v>81</v>
+        <v>83</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
-        <v>45557</v>
+        <v>45565</v>
       </c>
       <c r="B21" t="s">
         <v>22</v>
       </c>
       <c r="C21" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D21" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
-        <v>45537</v>
+        <v>45557</v>
       </c>
       <c r="B22" t="s">
         <v>22</v>
       </c>
       <c r="C22" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D22" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
-        <v>45533</v>
+        <v>45537</v>
       </c>
       <c r="B23" t="s">
         <v>22</v>
       </c>
       <c r="C23" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D23" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
-        <v>45509</v>
+        <v>45533</v>
       </c>
       <c r="B24" t="s">
         <v>22</v>
       </c>
       <c r="C24" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D24" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
-        <v>45504</v>
+        <v>45509</v>
       </c>
       <c r="B25" t="s">
         <v>22</v>
       </c>
       <c r="C25" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D25" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
-        <v>45490</v>
+        <v>45504</v>
       </c>
       <c r="B26" t="s">
         <v>22</v>
       </c>
       <c r="C26" t="s">
-        <v>69</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
+      </c>
+      <c r="D26" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
-        <v>45482</v>
+        <v>45490</v>
       </c>
       <c r="B27" t="s">
         <v>22</v>
       </c>
       <c r="C27" t="s">
-        <v>67</v>
-      </c>
-      <c r="D27" t="s">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
-        <v>45473</v>
+        <v>45482</v>
       </c>
       <c r="B28" t="s">
         <v>22</v>
       </c>
       <c r="C28" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D28" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
-        <v>45443</v>
+        <v>45473</v>
       </c>
       <c r="B29" t="s">
         <v>22</v>
       </c>
       <c r="C29" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D29" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
-        <v>45357</v>
+        <v>45443</v>
       </c>
       <c r="B30" t="s">
         <v>22</v>
       </c>
       <c r="C30" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D30" t="s">
-        <v>61</v>
-      </c>
-      <c r="E30" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
-        <v>45352</v>
+        <v>45357</v>
       </c>
       <c r="B31" t="s">
         <v>22</v>
       </c>
       <c r="C31" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D31" t="s">
-        <v>58</v>
+        <v>61</v>
+      </c>
+      <c r="E31" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
-        <v>45240</v>
+        <v>45352</v>
       </c>
       <c r="B32" t="s">
         <v>22</v>
       </c>
       <c r="C32" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D32" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
-        <v>45212</v>
+        <v>45240</v>
       </c>
       <c r="B33" t="s">
         <v>22</v>
       </c>
       <c r="C33" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D33" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
-        <v>45211</v>
-      </c>
-      <c r="B34" s="2" t="s">
+        <v>45212</v>
+      </c>
+      <c r="B34" t="s">
         <v>22</v>
       </c>
       <c r="C34" t="s">
-        <v>51</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
+      </c>
+      <c r="D34" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
-        <v>45147</v>
+        <v>45211</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C35" t="s">
-        <v>47</v>
-      </c>
-      <c r="D35" t="s">
-        <v>48</v>
-      </c>
-      <c r="E35" t="s">
-        <v>49</v>
+        <v>51</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
+        <v>45147</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C36" t="s">
+        <v>47</v>
+      </c>
+      <c r="D36" t="s">
+        <v>48</v>
+      </c>
+      <c r="E36" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A37" s="2">
         <v>45143</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C36" t="s">
+      <c r="B37" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C37" t="s">
         <v>44</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D37" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A37" s="2">
+    <row r="38" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A38" s="2">
         <v>45119</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C37" s="3" t="s">
+      <c r="B38" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D38" s="1" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A38" s="2">
-        <v>45113</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C38" t="s">
-        <v>26</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
-        <v>45112</v>
+        <v>45113</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C39" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
-        <v>45083</v>
+        <v>45112</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C40" t="s">
-        <v>12</v>
-      </c>
-      <c r="D40" t="s">
-        <v>3</v>
+        <v>28</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
-        <v>45082</v>
+        <v>45083</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C41" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D41" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
-        <v>45018</v>
+        <v>45082</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C42" t="s">
-        <v>54</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>55</v>
+        <v>13</v>
+      </c>
+      <c r="D42" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
-        <v>45014</v>
+        <v>45018</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C43" t="s">
-        <v>14</v>
-      </c>
-      <c r="D43" t="s">
-        <v>5</v>
+        <v>54</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
-        <v>44992</v>
+        <v>45014</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C44" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D44" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
-        <v>44959</v>
+        <v>44992</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C45" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D45" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
-        <v>44930</v>
+        <v>44959</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C46" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D46" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
-        <v>44897</v>
+        <v>44930</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C47" t="s">
-        <v>18</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
+      </c>
+      <c r="D47" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
-        <v>44682</v>
+        <v>44897</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C48" t="s">
-        <v>19</v>
-      </c>
-      <c r="D48" t="s">
-        <v>9</v>
+        <v>18</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
-        <v>44601</v>
+        <v>44682</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C49" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D49" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
-        <v>44725</v>
+        <v>44601</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C50" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D50" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
-        <v>44723</v>
+        <v>44725</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C51" t="s">
-        <v>42</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
+      </c>
+      <c r="D51" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
-        <v>44326</v>
+        <v>44723</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C52" t="s">
-        <v>38</v>
-      </c>
-      <c r="D52" t="s">
-        <v>39</v>
+        <v>42</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" s="2">
-        <v>44265</v>
+        <v>44326</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C53" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D53" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
-        <v>44148</v>
+        <v>44265</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C54" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D54" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" s="2">
-        <v>44146</v>
+        <v>44148</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C55" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D55" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
-        <v>44144</v>
+        <v>44146</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C56" t="s">
+        <v>32</v>
+      </c>
+      <c r="D56" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57" s="2">
+        <v>44144</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C57" t="s">
         <v>31</v>
       </c>
-      <c r="D56" t="s">
+      <c r="D57" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B57" s="2"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B58" s="2"/>
     </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B59" s="2"/>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A27:D47">
-    <sortCondition ref="B27:B47"/>
-    <sortCondition descending="1" ref="A27:A47"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A28:D48">
+    <sortCondition ref="B28:B48"/>
+    <sortCondition descending="1" ref="A28:A48"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="D47" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="D37" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="D38" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="D39" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="D51" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="D34" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="D42" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="D26" r:id="rId8" xr:uid="{FA3531C4-3B8B-4257-B20B-BB3BF511A818}"/>
-    <hyperlink ref="E19" r:id="rId9" xr:uid="{461EAE59-6B89-4B06-BC7F-5D62D70EDCD6}"/>
-    <hyperlink ref="D16" r:id="rId10" xr:uid="{9FC614FC-A94D-4784-8E8F-DFD619EA88C0}"/>
-    <hyperlink ref="D15" r:id="rId11" xr:uid="{0B29772C-F7FE-40CC-A257-2848F4518174}"/>
-    <hyperlink ref="E13" r:id="rId12" xr:uid="{C474B74F-3E03-433F-BC35-18768486A4FB}"/>
-    <hyperlink ref="E12" r:id="rId13" xr:uid="{209BE10C-36A4-4475-BDA6-365C34A7A7B4}"/>
-    <hyperlink ref="D11" r:id="rId14" xr:uid="{D908A389-6872-41E0-B81F-166FB55D55A3}"/>
-    <hyperlink ref="D10" r:id="rId15" xr:uid="{1BBDB9F5-EA33-4B8D-A13B-752105B1611A}"/>
+    <hyperlink ref="D48" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="D38" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="D39" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="D40" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="D52" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="D35" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="D43" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="D27" r:id="rId8" xr:uid="{FA3531C4-3B8B-4257-B20B-BB3BF511A818}"/>
+    <hyperlink ref="E20" r:id="rId9" xr:uid="{461EAE59-6B89-4B06-BC7F-5D62D70EDCD6}"/>
+    <hyperlink ref="D17" r:id="rId10" xr:uid="{9FC614FC-A94D-4784-8E8F-DFD619EA88C0}"/>
+    <hyperlink ref="D16" r:id="rId11" xr:uid="{0B29772C-F7FE-40CC-A257-2848F4518174}"/>
+    <hyperlink ref="E14" r:id="rId12" xr:uid="{C474B74F-3E03-433F-BC35-18768486A4FB}"/>
+    <hyperlink ref="E13" r:id="rId13" xr:uid="{209BE10C-36A4-4475-BDA6-365C34A7A7B4}"/>
+    <hyperlink ref="D12" r:id="rId14" xr:uid="{D908A389-6872-41E0-B81F-166FB55D55A3}"/>
+    <hyperlink ref="D11" r:id="rId15" xr:uid="{1BBDB9F5-EA33-4B8D-A13B-752105B1611A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId16"/>

--- a/data/posts.xlsx
+++ b/data/posts.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0F9AFD2-D95A-42D2-976E-EE0AE1D2436A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33CB6718-AB8A-459E-B85A-74B7B6DBCE01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4940" yWindow="4940" windowWidth="28800" windowHeight="15450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="125">
   <si>
     <t>date</t>
   </si>
@@ -400,6 +400,12 @@
   </si>
   <si>
     <t>Theoretical joint distribution of logrank test for PFS and OS</t>
+  </si>
+  <si>
+    <t>Edited book "Estimands in Clinical Trials"</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/posts/kasparrufibach_biostatistics-estimands-activity-7415005842665684992-iP7h?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAAQJ2qsB_r_XsYhAPWyf_WQeC5V6NOcbIXo</t>
   </si>
 </sst>
 </file>
@@ -742,7 +748,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.1796875" bestFit="1" customWidth="1"/>
@@ -771,58 +777,58 @@
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
-        <v>46001</v>
+        <v>46030</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
-        <v>45992</v>
+        <v>46001</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>117</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
+      </c>
+      <c r="D4" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
-        <v>45964</v>
+        <v>45989</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>113</v>
-      </c>
-      <c r="D5" t="s">
-        <v>114</v>
+        <v>117</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -833,768 +839,782 @@
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D6" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
-        <v>45959</v>
+        <v>45964</v>
       </c>
       <c r="B7" t="s">
         <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D7" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
-        <v>45956</v>
+        <v>45959</v>
       </c>
       <c r="B8" t="s">
         <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D8" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
-        <v>45941</v>
+        <v>45956</v>
       </c>
       <c r="B9" t="s">
         <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D9" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
-        <v>45927</v>
+        <v>45941</v>
       </c>
       <c r="B10" t="s">
         <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D10" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
-        <v>45871</v>
+        <v>45927</v>
       </c>
       <c r="B11" t="s">
         <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>103</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
+      </c>
+      <c r="D11" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
-        <v>45868</v>
+        <v>45871</v>
       </c>
       <c r="B12" t="s">
         <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
-        <v>45855</v>
+        <v>45868</v>
       </c>
       <c r="B13" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="D13" t="s">
-        <v>99</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>84</v>
+      <c r="C13" t="s">
+        <v>102</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
-        <v>45784</v>
+        <v>45855</v>
       </c>
       <c r="B14" t="s">
         <v>22</v>
       </c>
-      <c r="C14" t="s">
-        <v>96</v>
+      <c r="C14" s="5" t="s">
+        <v>100</v>
       </c>
       <c r="D14" t="s">
-        <v>97</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
-        <v>45725</v>
+        <v>45784</v>
       </c>
       <c r="B15" t="s">
         <v>22</v>
       </c>
       <c r="C15" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D15" t="s">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
-        <v>45696</v>
+        <v>45725</v>
       </c>
       <c r="B16" t="s">
         <v>22</v>
       </c>
       <c r="C16" t="s">
-        <v>93</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
+      </c>
+      <c r="D16" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
-        <v>45686</v>
+        <v>45696</v>
       </c>
       <c r="B17" t="s">
         <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
+        <v>45686</v>
+      </c>
+      <c r="B18" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" t="s">
+        <v>90</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="2">
         <v>45623</v>
       </c>
-      <c r="B18" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="B19" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" t="s">
         <v>89</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D19" t="s">
         <v>88</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" s="2">
-        <v>45584</v>
-      </c>
-      <c r="B19" t="s">
-        <v>22</v>
-      </c>
-      <c r="C19" t="s">
-        <v>87</v>
-      </c>
-      <c r="D19" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
-        <v>45568</v>
+        <v>45584</v>
       </c>
       <c r="B20" t="s">
         <v>22</v>
       </c>
-      <c r="C20" s="5" t="s">
-        <v>85</v>
+      <c r="C20" t="s">
+        <v>87</v>
       </c>
       <c r="D20" t="s">
-        <v>83</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
-        <v>45565</v>
+        <v>45568</v>
       </c>
       <c r="B21" t="s">
         <v>22</v>
       </c>
-      <c r="C21" t="s">
-        <v>82</v>
+      <c r="C21" s="5" t="s">
+        <v>85</v>
       </c>
       <c r="D21" t="s">
-        <v>81</v>
+        <v>83</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
-        <v>45557</v>
+        <v>45565</v>
       </c>
       <c r="B22" t="s">
         <v>22</v>
       </c>
       <c r="C22" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D22" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
-        <v>45537</v>
+        <v>45557</v>
       </c>
       <c r="B23" t="s">
         <v>22</v>
       </c>
       <c r="C23" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D23" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
-        <v>45533</v>
+        <v>45537</v>
       </c>
       <c r="B24" t="s">
         <v>22</v>
       </c>
       <c r="C24" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D24" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
-        <v>45509</v>
+        <v>45533</v>
       </c>
       <c r="B25" t="s">
         <v>22</v>
       </c>
       <c r="C25" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D25" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
-        <v>45504</v>
+        <v>45509</v>
       </c>
       <c r="B26" t="s">
         <v>22</v>
       </c>
       <c r="C26" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D26" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
-        <v>45490</v>
+        <v>45504</v>
       </c>
       <c r="B27" t="s">
         <v>22</v>
       </c>
       <c r="C27" t="s">
-        <v>69</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
+      </c>
+      <c r="D27" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
-        <v>45482</v>
+        <v>45490</v>
       </c>
       <c r="B28" t="s">
         <v>22</v>
       </c>
       <c r="C28" t="s">
-        <v>67</v>
-      </c>
-      <c r="D28" t="s">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
-        <v>45473</v>
+        <v>45482</v>
       </c>
       <c r="B29" t="s">
         <v>22</v>
       </c>
       <c r="C29" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D29" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
-        <v>45443</v>
+        <v>45473</v>
       </c>
       <c r="B30" t="s">
         <v>22</v>
       </c>
       <c r="C30" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D30" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
-        <v>45357</v>
+        <v>45443</v>
       </c>
       <c r="B31" t="s">
         <v>22</v>
       </c>
       <c r="C31" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D31" t="s">
-        <v>61</v>
-      </c>
-      <c r="E31" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
-        <v>45352</v>
+        <v>45357</v>
       </c>
       <c r="B32" t="s">
         <v>22</v>
       </c>
       <c r="C32" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D32" t="s">
-        <v>58</v>
+        <v>61</v>
+      </c>
+      <c r="E32" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
-        <v>45240</v>
+        <v>45352</v>
       </c>
       <c r="B33" t="s">
         <v>22</v>
       </c>
       <c r="C33" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D33" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
-        <v>45212</v>
+        <v>45240</v>
       </c>
       <c r="B34" t="s">
         <v>22</v>
       </c>
       <c r="C34" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D34" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
-        <v>45211</v>
-      </c>
-      <c r="B35" s="2" t="s">
+        <v>45212</v>
+      </c>
+      <c r="B35" t="s">
         <v>22</v>
       </c>
       <c r="C35" t="s">
-        <v>51</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
+      </c>
+      <c r="D35" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
-        <v>45147</v>
+        <v>45211</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C36" t="s">
-        <v>47</v>
-      </c>
-      <c r="D36" t="s">
-        <v>48</v>
-      </c>
-      <c r="E36" t="s">
-        <v>49</v>
+        <v>51</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
+        <v>45147</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C37" t="s">
+        <v>47</v>
+      </c>
+      <c r="D37" t="s">
+        <v>48</v>
+      </c>
+      <c r="E37" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A38" s="2">
         <v>45143</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C37" t="s">
+      <c r="B38" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C38" t="s">
         <v>44</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D38" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A38" s="2">
+    <row r="39" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A39" s="2">
         <v>45119</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C38" s="3" t="s">
+      <c r="B39" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="D39" s="1" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A39" s="2">
-        <v>45113</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C39" t="s">
-        <v>26</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
-        <v>45112</v>
+        <v>45113</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C40" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
-        <v>45083</v>
+        <v>45112</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C41" t="s">
-        <v>12</v>
-      </c>
-      <c r="D41" t="s">
-        <v>3</v>
+        <v>28</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
-        <v>45082</v>
+        <v>45083</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C42" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D42" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
-        <v>45018</v>
+        <v>45082</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C43" t="s">
-        <v>54</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>55</v>
+        <v>13</v>
+      </c>
+      <c r="D43" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
-        <v>45014</v>
+        <v>45018</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C44" t="s">
-        <v>14</v>
-      </c>
-      <c r="D44" t="s">
-        <v>5</v>
+        <v>54</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
-        <v>44992</v>
+        <v>45014</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C45" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D45" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
-        <v>44959</v>
+        <v>44992</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D46" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
-        <v>44930</v>
+        <v>44959</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C47" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D47" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
-        <v>44897</v>
+        <v>44930</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C48" t="s">
-        <v>18</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
+      </c>
+      <c r="D48" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
-        <v>44682</v>
+        <v>44897</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C49" t="s">
-        <v>19</v>
-      </c>
-      <c r="D49" t="s">
-        <v>9</v>
+        <v>18</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
-        <v>44601</v>
+        <v>44682</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C50" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D50" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
-        <v>44725</v>
+        <v>44601</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C51" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D51" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
-        <v>44723</v>
+        <v>44725</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C52" t="s">
-        <v>42</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
+      </c>
+      <c r="D52" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" s="2">
-        <v>44326</v>
+        <v>44723</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C53" t="s">
-        <v>38</v>
-      </c>
-      <c r="D53" t="s">
-        <v>39</v>
+        <v>42</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
-        <v>44265</v>
+        <v>44326</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C54" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D54" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" s="2">
-        <v>44148</v>
+        <v>44265</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C55" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D55" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
-        <v>44146</v>
+        <v>44148</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C56" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D56" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" s="2">
-        <v>44144</v>
+        <v>44146</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C57" t="s">
+        <v>32</v>
+      </c>
+      <c r="D57" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58" s="2">
+        <v>44144</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C58" t="s">
         <v>31</v>
       </c>
-      <c r="D57" t="s">
+      <c r="D58" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B58" s="2"/>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B59" s="2"/>
     </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B60" s="2"/>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A28:D48">
-    <sortCondition ref="B28:B48"/>
-    <sortCondition descending="1" ref="A28:A48"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A29:D49">
+    <sortCondition ref="B29:B49"/>
+    <sortCondition descending="1" ref="A29:A49"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="D48" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="D38" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="D39" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="D40" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="D52" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="D35" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="D43" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="D27" r:id="rId8" xr:uid="{FA3531C4-3B8B-4257-B20B-BB3BF511A818}"/>
-    <hyperlink ref="E20" r:id="rId9" xr:uid="{461EAE59-6B89-4B06-BC7F-5D62D70EDCD6}"/>
-    <hyperlink ref="D17" r:id="rId10" xr:uid="{9FC614FC-A94D-4784-8E8F-DFD619EA88C0}"/>
-    <hyperlink ref="D16" r:id="rId11" xr:uid="{0B29772C-F7FE-40CC-A257-2848F4518174}"/>
-    <hyperlink ref="E14" r:id="rId12" xr:uid="{C474B74F-3E03-433F-BC35-18768486A4FB}"/>
-    <hyperlink ref="E13" r:id="rId13" xr:uid="{209BE10C-36A4-4475-BDA6-365C34A7A7B4}"/>
-    <hyperlink ref="D12" r:id="rId14" xr:uid="{D908A389-6872-41E0-B81F-166FB55D55A3}"/>
-    <hyperlink ref="D11" r:id="rId15" xr:uid="{1BBDB9F5-EA33-4B8D-A13B-752105B1611A}"/>
+    <hyperlink ref="D49" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="D39" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="D40" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="D41" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="D53" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="D36" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="D44" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="D28" r:id="rId8" xr:uid="{FA3531C4-3B8B-4257-B20B-BB3BF511A818}"/>
+    <hyperlink ref="E21" r:id="rId9" xr:uid="{461EAE59-6B89-4B06-BC7F-5D62D70EDCD6}"/>
+    <hyperlink ref="D18" r:id="rId10" xr:uid="{9FC614FC-A94D-4784-8E8F-DFD619EA88C0}"/>
+    <hyperlink ref="D17" r:id="rId11" xr:uid="{0B29772C-F7FE-40CC-A257-2848F4518174}"/>
+    <hyperlink ref="E15" r:id="rId12" xr:uid="{C474B74F-3E03-433F-BC35-18768486A4FB}"/>
+    <hyperlink ref="E14" r:id="rId13" xr:uid="{209BE10C-36A4-4475-BDA6-365C34A7A7B4}"/>
+    <hyperlink ref="D13" r:id="rId14" xr:uid="{D908A389-6872-41E0-B81F-166FB55D55A3}"/>
+    <hyperlink ref="D12" r:id="rId15" xr:uid="{1BBDB9F5-EA33-4B8D-A13B-752105B1611A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId16"/>

--- a/data/posts.xlsx
+++ b/data/posts.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33CB6718-AB8A-459E-B85A-74B7B6DBCE01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{362121FD-434B-45B5-80CF-E1D7AF452CD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="127">
   <si>
     <t>date</t>
   </si>
@@ -406,6 +406,12 @@
   </si>
   <si>
     <t>https://www.linkedin.com/posts/kasparrufibach_biostatistics-estimands-activity-7415005842665684992-iP7h?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAAQJ2qsB_r_XsYhAPWyf_WQeC5V6NOcbIXo</t>
+  </si>
+  <si>
+    <t>Opening of registration of 11th EFSPI regulatory statistics workshop</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/posts/kasparrufibach_we-did-it-again-the-registration-for-the-activity-7434543762435043330-myiL?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAAQJ2qsB_r_XsYhAPWyf_WQeC5V6NOcbIXo</t>
   </si>
 </sst>
 </file>
@@ -748,17 +754,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E60"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:E61"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="106.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="106.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="223" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="99.453125" customWidth="1"/>
+    <col min="5" max="5" width="99.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -775,77 +781,77 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
+        <v>46084</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
         <v>46030</v>
       </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
         <v>123</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D3" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="2">
+    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
         <v>46001</v>
       </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
         <v>122</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D4" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="2">
+    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
         <v>45992</v>
       </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
         <v>118</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D5" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="2">
+    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
         <v>45989</v>
       </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
         <v>117</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="2">
-        <v>45964</v>
-      </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" t="s">
-        <v>113</v>
-      </c>
-      <c r="D6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>45964</v>
       </c>
@@ -853,768 +859,782 @@
         <v>22</v>
       </c>
       <c r="C7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D7" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>45964</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
         <v>112</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D8" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="2">
+    <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
         <v>45959</v>
       </c>
-      <c r="B8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
         <v>116</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D9" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="2">
+    <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
         <v>45956</v>
       </c>
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" t="s">
         <v>109</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D10" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="2">
+    <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
         <v>45941</v>
       </c>
-      <c r="B10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" t="s">
         <v>107</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D11" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="2">
+    <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
         <v>45927</v>
       </c>
-      <c r="B11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" t="s">
         <v>106</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D12" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="2">
+    <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
         <v>45871</v>
       </c>
-      <c r="B12" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" t="s">
         <v>103</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="2">
+    <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
         <v>45868</v>
       </c>
-      <c r="B13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="B14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" t="s">
         <v>102</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="2">
+    <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
         <v>45855</v>
       </c>
-      <c r="B14" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" s="5" t="s">
+      <c r="B15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D15" t="s">
         <v>99</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E15" s="4" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="2">
+    <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
         <v>45784</v>
       </c>
-      <c r="B15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="B16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" t="s">
         <v>96</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D16" t="s">
         <v>97</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E16" s="1" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="2">
+    <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
         <v>45725</v>
       </c>
-      <c r="B16" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="B17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" t="s">
         <v>94</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D17" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="2">
+    <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
         <v>45696</v>
       </c>
-      <c r="B17" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="B18" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" t="s">
         <v>93</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D18" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="2">
+    <row r="19" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
         <v>45686</v>
       </c>
-      <c r="B18" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="B19" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" t="s">
         <v>90</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D19" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="2">
+    <row r="20" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
         <v>45623</v>
       </c>
-      <c r="B19" t="s">
-        <v>22</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="B20" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" t="s">
         <v>89</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D20" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" s="2">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
         <v>45584</v>
       </c>
-      <c r="B20" t="s">
-        <v>22</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="B21" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" t="s">
         <v>87</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D21" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" s="2">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
         <v>45568</v>
       </c>
-      <c r="B21" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" s="5" t="s">
+      <c r="B22" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D22" t="s">
         <v>83</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E22" s="4" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A22" s="2">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
         <v>45565</v>
       </c>
-      <c r="B22" t="s">
-        <v>22</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="B23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" t="s">
         <v>82</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D23" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A23" s="2">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
         <v>45557</v>
       </c>
-      <c r="B23" t="s">
-        <v>22</v>
-      </c>
-      <c r="C23" t="s">
+      <c r="B24" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" t="s">
         <v>79</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D24" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A24" s="2">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
         <v>45537</v>
       </c>
-      <c r="B24" t="s">
-        <v>22</v>
-      </c>
-      <c r="C24" t="s">
+      <c r="B25" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25" t="s">
         <v>77</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D25" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A25" s="2">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
         <v>45533</v>
       </c>
-      <c r="B25" t="s">
-        <v>22</v>
-      </c>
-      <c r="C25" t="s">
+      <c r="B26" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" t="s">
         <v>75</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D26" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A26" s="2">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
         <v>45509</v>
       </c>
-      <c r="B26" t="s">
-        <v>22</v>
-      </c>
-      <c r="C26" t="s">
+      <c r="B27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C27" t="s">
         <v>71</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D27" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A27" s="2">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
         <v>45504</v>
       </c>
-      <c r="B27" t="s">
-        <v>22</v>
-      </c>
-      <c r="C27" t="s">
+      <c r="B28" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" t="s">
         <v>73</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D28" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A28" s="2">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
         <v>45490</v>
       </c>
-      <c r="B28" t="s">
-        <v>22</v>
-      </c>
-      <c r="C28" t="s">
+      <c r="B29" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29" t="s">
         <v>69</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D29" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A29" s="2">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
         <v>45482</v>
       </c>
-      <c r="B29" t="s">
-        <v>22</v>
-      </c>
-      <c r="C29" t="s">
+      <c r="B30" t="s">
+        <v>22</v>
+      </c>
+      <c r="C30" t="s">
         <v>67</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D30" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A30" s="2">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
         <v>45473</v>
       </c>
-      <c r="B30" t="s">
-        <v>22</v>
-      </c>
-      <c r="C30" t="s">
+      <c r="B31" t="s">
+        <v>22</v>
+      </c>
+      <c r="C31" t="s">
         <v>65</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D31" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A31" s="2">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
         <v>45443</v>
       </c>
-      <c r="B31" t="s">
-        <v>22</v>
-      </c>
-      <c r="C31" t="s">
+      <c r="B32" t="s">
+        <v>22</v>
+      </c>
+      <c r="C32" t="s">
         <v>63</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D32" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A32" s="2">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
         <v>45357</v>
       </c>
-      <c r="B32" t="s">
-        <v>22</v>
-      </c>
-      <c r="C32" t="s">
+      <c r="B33" t="s">
+        <v>22</v>
+      </c>
+      <c r="C33" t="s">
         <v>60</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D33" t="s">
         <v>61</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E33" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A33" s="2">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
         <v>45352</v>
       </c>
-      <c r="B33" t="s">
-        <v>22</v>
-      </c>
-      <c r="C33" t="s">
+      <c r="B34" t="s">
+        <v>22</v>
+      </c>
+      <c r="C34" t="s">
         <v>59</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D34" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A34" s="2">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
         <v>45240</v>
       </c>
-      <c r="B34" t="s">
-        <v>22</v>
-      </c>
-      <c r="C34" t="s">
+      <c r="B35" t="s">
+        <v>22</v>
+      </c>
+      <c r="C35" t="s">
         <v>57</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D35" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A35" s="2">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
         <v>45212</v>
       </c>
-      <c r="B35" t="s">
-        <v>22</v>
-      </c>
-      <c r="C35" t="s">
+      <c r="B36" t="s">
+        <v>22</v>
+      </c>
+      <c r="C36" t="s">
         <v>53</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D36" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A36" s="2">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
         <v>45211</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C36" t="s">
+      <c r="B37" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C37" t="s">
         <v>51</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D37" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A37" s="2">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
         <v>45147</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C37" t="s">
+      <c r="B38" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C38" t="s">
         <v>47</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D38" t="s">
         <v>48</v>
       </c>
-      <c r="E37" t="s">
+      <c r="E38" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A38" s="2">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="2">
         <v>45143</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C38" t="s">
+      <c r="B39" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C39" t="s">
         <v>44</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D39" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A39" s="2">
+    <row r="40" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A40" s="2">
         <v>45119</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C39" s="3" t="s">
+      <c r="B40" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="D40" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A40" s="2">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="2">
         <v>45113</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C40" t="s">
+      <c r="B41" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" t="s">
         <v>26</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="D41" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A41" s="2">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
         <v>45112</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C41" t="s">
+      <c r="B42" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C42" t="s">
         <v>28</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D42" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A42" s="2">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="2">
         <v>45083</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C42" t="s">
+      <c r="B43" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C43" t="s">
         <v>12</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D43" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A43" s="2">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
         <v>45082</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C43" t="s">
+      <c r="B44" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C44" t="s">
         <v>13</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D44" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A44" s="2">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="2">
         <v>45018</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C44" t="s">
+      <c r="B45" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C45" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="D45" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A45" s="2">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="2">
         <v>45014</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C45" t="s">
+      <c r="B46" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C46" t="s">
         <v>14</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D46" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A46" s="2">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="2">
         <v>44992</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C46" t="s">
+      <c r="B47" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C47" t="s">
         <v>15</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D47" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A47" s="2">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="2">
         <v>44959</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C47" t="s">
+      <c r="B48" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C48" t="s">
         <v>16</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D48" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A48" s="2">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="2">
         <v>44930</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C48" t="s">
+      <c r="B49" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C49" t="s">
         <v>17</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D49" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" s="2">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="2">
         <v>44897</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C49" t="s">
+      <c r="B50" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C50" t="s">
         <v>18</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="D50" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" s="2">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="2">
         <v>44682</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C50" t="s">
+      <c r="B51" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C51" t="s">
         <v>19</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D51" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" s="2">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="2">
         <v>44601</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C51" t="s">
+      <c r="B52" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C52" t="s">
         <v>20</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D52" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" s="2">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="2">
         <v>44725</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C52" t="s">
-        <v>40</v>
-      </c>
-      <c r="D52" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" s="2">
-        <v>44723</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C53" t="s">
-        <v>42</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+        <v>40</v>
+      </c>
+      <c r="D53" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
-        <v>44326</v>
+        <v>44723</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C54" t="s">
-        <v>38</v>
-      </c>
-      <c r="D54" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+        <v>42</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
-        <v>44265</v>
+        <v>44326</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C55" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D55" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
-        <v>44148</v>
+        <v>44265</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C56" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D56" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
-        <v>44146</v>
+        <v>44148</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C57" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D57" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
-        <v>44144</v>
+        <v>44146</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C58" t="s">
+        <v>32</v>
+      </c>
+      <c r="D58" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="2">
+        <v>44144</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C59" t="s">
         <v>31</v>
       </c>
-      <c r="D58" t="s">
+      <c r="D59" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B59" s="2"/>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B60" s="2"/>
     </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B61" s="2"/>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A29:D49">
-    <sortCondition ref="B29:B49"/>
-    <sortCondition descending="1" ref="A29:A49"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A30:D50">
+    <sortCondition ref="B30:B50"/>
+    <sortCondition descending="1" ref="A30:A50"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="D49" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="D39" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="D40" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="D41" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="D53" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="D36" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="D44" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="D28" r:id="rId8" xr:uid="{FA3531C4-3B8B-4257-B20B-BB3BF511A818}"/>
-    <hyperlink ref="E21" r:id="rId9" xr:uid="{461EAE59-6B89-4B06-BC7F-5D62D70EDCD6}"/>
-    <hyperlink ref="D18" r:id="rId10" xr:uid="{9FC614FC-A94D-4784-8E8F-DFD619EA88C0}"/>
-    <hyperlink ref="D17" r:id="rId11" xr:uid="{0B29772C-F7FE-40CC-A257-2848F4518174}"/>
-    <hyperlink ref="E15" r:id="rId12" xr:uid="{C474B74F-3E03-433F-BC35-18768486A4FB}"/>
-    <hyperlink ref="E14" r:id="rId13" xr:uid="{209BE10C-36A4-4475-BDA6-365C34A7A7B4}"/>
-    <hyperlink ref="D13" r:id="rId14" xr:uid="{D908A389-6872-41E0-B81F-166FB55D55A3}"/>
-    <hyperlink ref="D12" r:id="rId15" xr:uid="{1BBDB9F5-EA33-4B8D-A13B-752105B1611A}"/>
+    <hyperlink ref="D50" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="D40" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="D41" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="D42" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="D54" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="D37" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="D45" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="D29" r:id="rId8" xr:uid="{FA3531C4-3B8B-4257-B20B-BB3BF511A818}"/>
+    <hyperlink ref="E22" r:id="rId9" xr:uid="{461EAE59-6B89-4B06-BC7F-5D62D70EDCD6}"/>
+    <hyperlink ref="D19" r:id="rId10" xr:uid="{9FC614FC-A94D-4784-8E8F-DFD619EA88C0}"/>
+    <hyperlink ref="D18" r:id="rId11" xr:uid="{0B29772C-F7FE-40CC-A257-2848F4518174}"/>
+    <hyperlink ref="E16" r:id="rId12" xr:uid="{C474B74F-3E03-433F-BC35-18768486A4FB}"/>
+    <hyperlink ref="E15" r:id="rId13" xr:uid="{209BE10C-36A4-4475-BDA6-365C34A7A7B4}"/>
+    <hyperlink ref="D14" r:id="rId14" xr:uid="{D908A389-6872-41E0-B81F-166FB55D55A3}"/>
+    <hyperlink ref="D13" r:id="rId15" xr:uid="{1BBDB9F5-EA33-4B8D-A13B-752105B1611A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId16"/>

--- a/data/posts.xlsx
+++ b/data/posts.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{362121FD-434B-45B5-80CF-E1D7AF452CD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{512BBFF8-A184-4E5A-A17E-AE42A50BA3C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="129">
   <si>
     <t>date</t>
   </si>
@@ -412,6 +412,12 @@
   </si>
   <si>
     <t>https://www.linkedin.com/posts/kasparrufibach_we-did-it-again-the-registration-for-the-activity-7434543762435043330-myiL?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAAQJ2qsB_r_XsYhAPWyf_WQeC5V6NOcbIXo</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/posts/kasparrufibach_tldr-we-want-to-analyze-trials-in-real-ugcPost-7456645705613508609-1AjI?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAAQJ2qsB_r_XsYhAPWyf_WQeC5V6NOcbIXo</t>
+  </si>
+  <si>
+    <t>Some questions on FDA's real time trial monitoring announcement</t>
   </si>
 </sst>
 </file>
@@ -754,17 +760,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E61"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E62"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="106.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="106.7265625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="223" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="99.42578125" customWidth="1"/>
+    <col min="5" max="5" width="99.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -781,91 +787,91 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
+        <v>46145</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2">
         <v>46084</v>
       </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
         <v>125</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D3" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
+    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="2">
         <v>46030</v>
       </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
         <v>123</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D4" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
+    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="2">
         <v>46001</v>
       </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
         <v>122</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D5" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
+    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="2">
         <v>45992</v>
       </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
         <v>118</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D6" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
+    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2">
         <v>45989</v>
       </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
         <v>117</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
-        <v>45964</v>
-      </c>
-      <c r="B7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" t="s">
-        <v>113</v>
-      </c>
-      <c r="D7" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>45964</v>
       </c>
@@ -873,768 +879,782 @@
         <v>22</v>
       </c>
       <c r="C8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D8" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="2">
+        <v>45964</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
         <v>112</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D9" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
+    <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="2">
         <v>45959</v>
       </c>
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" t="s">
         <v>116</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D10" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
+    <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="2">
         <v>45956</v>
       </c>
-      <c r="B10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" t="s">
         <v>109</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D11" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
+    <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="2">
         <v>45941</v>
       </c>
-      <c r="B11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" t="s">
         <v>107</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D12" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
+    <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="2">
         <v>45927</v>
       </c>
-      <c r="B12" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" t="s">
         <v>106</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D13" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
+    <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="2">
         <v>45871</v>
       </c>
-      <c r="B13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="B14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" t="s">
         <v>103</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
+    <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="2">
         <v>45868</v>
       </c>
-      <c r="B14" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="B15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" t="s">
         <v>102</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D15" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
+    <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="2">
         <v>45855</v>
       </c>
-      <c r="B15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="5" t="s">
+      <c r="B16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D16" t="s">
         <v>99</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E16" s="4" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2">
+    <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="2">
         <v>45784</v>
       </c>
-      <c r="B16" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="B17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" t="s">
         <v>96</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D17" t="s">
         <v>97</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E17" s="1" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
+    <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="2">
         <v>45725</v>
       </c>
-      <c r="B17" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="B18" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" t="s">
         <v>94</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D18" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
+    <row r="19" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="2">
         <v>45696</v>
       </c>
-      <c r="B18" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="B19" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" t="s">
         <v>93</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D19" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
+    <row r="20" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="2">
         <v>45686</v>
       </c>
-      <c r="B19" t="s">
-        <v>22</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="B20" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" t="s">
         <v>90</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D20" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
+    <row r="21" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="2">
         <v>45623</v>
       </c>
-      <c r="B20" t="s">
-        <v>22</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="B21" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" t="s">
         <v>89</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D21" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" s="2">
         <v>45584</v>
       </c>
-      <c r="B21" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="B22" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" t="s">
         <v>87</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D22" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="2">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" s="2">
         <v>45568</v>
       </c>
-      <c r="B22" t="s">
-        <v>22</v>
-      </c>
-      <c r="C22" s="5" t="s">
+      <c r="B23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D23" t="s">
         <v>83</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E23" s="4" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" s="2">
         <v>45565</v>
       </c>
-      <c r="B23" t="s">
-        <v>22</v>
-      </c>
-      <c r="C23" t="s">
+      <c r="B24" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" t="s">
         <v>82</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D24" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="2">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" s="2">
         <v>45557</v>
       </c>
-      <c r="B24" t="s">
-        <v>22</v>
-      </c>
-      <c r="C24" t="s">
+      <c r="B25" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25" t="s">
         <v>79</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D25" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="2">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" s="2">
         <v>45537</v>
       </c>
-      <c r="B25" t="s">
-        <v>22</v>
-      </c>
-      <c r="C25" t="s">
+      <c r="B26" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" t="s">
         <v>77</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D26" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="2">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" s="2">
         <v>45533</v>
       </c>
-      <c r="B26" t="s">
-        <v>22</v>
-      </c>
-      <c r="C26" t="s">
+      <c r="B27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C27" t="s">
         <v>75</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D27" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="2">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28" s="2">
         <v>45509</v>
       </c>
-      <c r="B27" t="s">
-        <v>22</v>
-      </c>
-      <c r="C27" t="s">
+      <c r="B28" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" t="s">
         <v>71</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D28" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="2">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" s="2">
         <v>45504</v>
       </c>
-      <c r="B28" t="s">
-        <v>22</v>
-      </c>
-      <c r="C28" t="s">
+      <c r="B29" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29" t="s">
         <v>73</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D29" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="2">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" s="2">
         <v>45490</v>
       </c>
-      <c r="B29" t="s">
-        <v>22</v>
-      </c>
-      <c r="C29" t="s">
+      <c r="B30" t="s">
+        <v>22</v>
+      </c>
+      <c r="C30" t="s">
         <v>69</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D30" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="2">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" s="2">
         <v>45482</v>
       </c>
-      <c r="B30" t="s">
-        <v>22</v>
-      </c>
-      <c r="C30" t="s">
+      <c r="B31" t="s">
+        <v>22</v>
+      </c>
+      <c r="C31" t="s">
         <v>67</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D31" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="2">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32" s="2">
         <v>45473</v>
       </c>
-      <c r="B31" t="s">
-        <v>22</v>
-      </c>
-      <c r="C31" t="s">
+      <c r="B32" t="s">
+        <v>22</v>
+      </c>
+      <c r="C32" t="s">
         <v>65</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D32" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="2">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A33" s="2">
         <v>45443</v>
       </c>
-      <c r="B32" t="s">
-        <v>22</v>
-      </c>
-      <c r="C32" t="s">
+      <c r="B33" t="s">
+        <v>22</v>
+      </c>
+      <c r="C33" t="s">
         <v>63</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D33" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="2">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A34" s="2">
         <v>45357</v>
       </c>
-      <c r="B33" t="s">
-        <v>22</v>
-      </c>
-      <c r="C33" t="s">
+      <c r="B34" t="s">
+        <v>22</v>
+      </c>
+      <c r="C34" t="s">
         <v>60</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D34" t="s">
         <v>61</v>
       </c>
-      <c r="E33" t="s">
+      <c r="E34" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="2">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A35" s="2">
         <v>45352</v>
       </c>
-      <c r="B34" t="s">
-        <v>22</v>
-      </c>
-      <c r="C34" t="s">
+      <c r="B35" t="s">
+        <v>22</v>
+      </c>
+      <c r="C35" t="s">
         <v>59</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D35" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="2">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A36" s="2">
         <v>45240</v>
       </c>
-      <c r="B35" t="s">
-        <v>22</v>
-      </c>
-      <c r="C35" t="s">
+      <c r="B36" t="s">
+        <v>22</v>
+      </c>
+      <c r="C36" t="s">
         <v>57</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D36" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="2">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A37" s="2">
         <v>45212</v>
       </c>
-      <c r="B36" t="s">
-        <v>22</v>
-      </c>
-      <c r="C36" t="s">
+      <c r="B37" t="s">
+        <v>22</v>
+      </c>
+      <c r="C37" t="s">
         <v>53</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D37" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="2">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A38" s="2">
         <v>45211</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C37" t="s">
+      <c r="B38" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C38" t="s">
         <v>51</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D38" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="2">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A39" s="2">
         <v>45147</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C38" t="s">
+      <c r="B39" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C39" t="s">
         <v>47</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D39" t="s">
         <v>48</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E39" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="2">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A40" s="2">
         <v>45143</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C39" t="s">
+      <c r="B40" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C40" t="s">
         <v>44</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D40" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A40" s="2">
+    <row r="41" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A41" s="2">
         <v>45119</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C40" s="3" t="s">
+      <c r="B41" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="D41" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="2">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A42" s="2">
         <v>45113</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C41" t="s">
+      <c r="B42" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C42" t="s">
         <v>26</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D42" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="2">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A43" s="2">
         <v>45112</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C42" t="s">
+      <c r="B43" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C43" t="s">
         <v>28</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="D43" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="2">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A44" s="2">
         <v>45083</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C43" t="s">
+      <c r="B44" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C44" t="s">
         <v>12</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D44" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="2">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A45" s="2">
         <v>45082</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C44" t="s">
+      <c r="B45" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C45" t="s">
         <v>13</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D45" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="2">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A46" s="2">
         <v>45018</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C45" t="s">
+      <c r="B46" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C46" t="s">
         <v>54</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="D46" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="2">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A47" s="2">
         <v>45014</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C46" t="s">
+      <c r="B47" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C47" t="s">
         <v>14</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D47" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="2">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A48" s="2">
         <v>44992</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C47" t="s">
+      <c r="B48" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C48" t="s">
         <v>15</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D48" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="2">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49" s="2">
         <v>44959</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C48" t="s">
+      <c r="B49" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C49" t="s">
         <v>16</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D49" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="2">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50" s="2">
         <v>44930</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C49" t="s">
+      <c r="B50" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C50" t="s">
         <v>17</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D50" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="2">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51" s="2">
         <v>44897</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C50" t="s">
+      <c r="B51" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C51" t="s">
         <v>18</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="D51" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="2">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52" s="2">
         <v>44682</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C51" t="s">
+      <c r="B52" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C52" t="s">
         <v>19</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D52" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="2">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53" s="2">
         <v>44601</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C52" t="s">
+      <c r="B53" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C53" t="s">
         <v>20</v>
       </c>
-      <c r="D52" t="s">
+      <c r="D53" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="2">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54" s="2">
         <v>44725</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C53" t="s">
-        <v>40</v>
-      </c>
-      <c r="D53" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="2">
-        <v>44723</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C54" t="s">
-        <v>42</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+      <c r="D54" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" s="2">
-        <v>44326</v>
+        <v>44723</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C55" t="s">
-        <v>38</v>
-      </c>
-      <c r="D55" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
-        <v>44265</v>
+        <v>44326</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C56" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D56" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" s="2">
-        <v>44148</v>
+        <v>44265</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C57" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D57" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
-        <v>44146</v>
+        <v>44148</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C58" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D58" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" s="2">
-        <v>44144</v>
+        <v>44146</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C59" t="s">
+        <v>32</v>
+      </c>
+      <c r="D59" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60" s="2">
+        <v>44144</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C60" t="s">
         <v>31</v>
       </c>
-      <c r="D59" t="s">
+      <c r="D60" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B60" s="2"/>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B61" s="2"/>
     </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B62" s="2"/>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A30:D50">
-    <sortCondition ref="B30:B50"/>
-    <sortCondition descending="1" ref="A30:A50"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A31:D51">
+    <sortCondition ref="B31:B51"/>
+    <sortCondition descending="1" ref="A31:A51"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="D50" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="D40" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="D41" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="D42" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="D54" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="D37" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="D45" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="D29" r:id="rId8" xr:uid="{FA3531C4-3B8B-4257-B20B-BB3BF511A818}"/>
-    <hyperlink ref="E22" r:id="rId9" xr:uid="{461EAE59-6B89-4B06-BC7F-5D62D70EDCD6}"/>
-    <hyperlink ref="D19" r:id="rId10" xr:uid="{9FC614FC-A94D-4784-8E8F-DFD619EA88C0}"/>
-    <hyperlink ref="D18" r:id="rId11" xr:uid="{0B29772C-F7FE-40CC-A257-2848F4518174}"/>
-    <hyperlink ref="E16" r:id="rId12" xr:uid="{C474B74F-3E03-433F-BC35-18768486A4FB}"/>
-    <hyperlink ref="E15" r:id="rId13" xr:uid="{209BE10C-36A4-4475-BDA6-365C34A7A7B4}"/>
-    <hyperlink ref="D14" r:id="rId14" xr:uid="{D908A389-6872-41E0-B81F-166FB55D55A3}"/>
-    <hyperlink ref="D13" r:id="rId15" xr:uid="{1BBDB9F5-EA33-4B8D-A13B-752105B1611A}"/>
+    <hyperlink ref="D51" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="D41" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="D42" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="D43" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="D55" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="D38" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="D46" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="D30" r:id="rId8" xr:uid="{FA3531C4-3B8B-4257-B20B-BB3BF511A818}"/>
+    <hyperlink ref="E23" r:id="rId9" xr:uid="{461EAE59-6B89-4B06-BC7F-5D62D70EDCD6}"/>
+    <hyperlink ref="D20" r:id="rId10" xr:uid="{9FC614FC-A94D-4784-8E8F-DFD619EA88C0}"/>
+    <hyperlink ref="D19" r:id="rId11" xr:uid="{0B29772C-F7FE-40CC-A257-2848F4518174}"/>
+    <hyperlink ref="E17" r:id="rId12" xr:uid="{C474B74F-3E03-433F-BC35-18768486A4FB}"/>
+    <hyperlink ref="E16" r:id="rId13" xr:uid="{209BE10C-36A4-4475-BDA6-365C34A7A7B4}"/>
+    <hyperlink ref="D15" r:id="rId14" xr:uid="{D908A389-6872-41E0-B81F-166FB55D55A3}"/>
+    <hyperlink ref="D14" r:id="rId15" xr:uid="{1BBDB9F5-EA33-4B8D-A13B-752105B1611A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId16"/>

--- a/data/posts.xlsx
+++ b/data/posts.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{512BBFF8-A184-4E5A-A17E-AE42A50BA3C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53ACF88F-A373-4C10-8E33-3DAE1FC87037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="131">
   <si>
     <t>date</t>
   </si>
@@ -418,6 +418,12 @@
   </si>
   <si>
     <t>Some questions on FDA's real time trial monitoring announcement</t>
+  </si>
+  <si>
+    <t>Communication challenges for complex designs</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/posts/kasparrufibach_biostatistics-inference-clinicaltrials-share-7457711254632079362-rNIo?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAAQJ2qsB_r_XsYhAPWyf_WQeC5V6NOcbIXo</t>
   </si>
 </sst>
 </file>
@@ -760,7 +766,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.1796875" bestFit="1" customWidth="1"/>
@@ -789,100 +795,100 @@
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
-        <v>46145</v>
+        <v>46148</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D2" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
-        <v>46084</v>
+        <v>46145</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
-        <v>46030</v>
+        <v>46084</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
-        <v>46001</v>
+        <v>46030</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D5" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
-        <v>45992</v>
+        <v>46001</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B7" t="s">
         <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>117</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
+      </c>
+      <c r="D7" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
-        <v>45964</v>
+        <v>45989</v>
       </c>
       <c r="B8" t="s">
         <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>113</v>
-      </c>
-      <c r="D8" t="s">
-        <v>114</v>
+        <v>117</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -893,768 +899,782 @@
         <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D9" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
-        <v>45959</v>
+        <v>45964</v>
       </c>
       <c r="B10" t="s">
         <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D10" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
-        <v>45956</v>
+        <v>45959</v>
       </c>
       <c r="B11" t="s">
         <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D11" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
-        <v>45941</v>
+        <v>45956</v>
       </c>
       <c r="B12" t="s">
         <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D12" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
-        <v>45927</v>
+        <v>45941</v>
       </c>
       <c r="B13" t="s">
         <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D13" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
-        <v>45871</v>
+        <v>45927</v>
       </c>
       <c r="B14" t="s">
         <v>22</v>
       </c>
       <c r="C14" t="s">
-        <v>103</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
+      </c>
+      <c r="D14" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
-        <v>45868</v>
+        <v>45871</v>
       </c>
       <c r="B15" t="s">
         <v>22</v>
       </c>
       <c r="C15" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
-        <v>45855</v>
+        <v>45868</v>
       </c>
       <c r="B16" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="D16" t="s">
-        <v>99</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>84</v>
+      <c r="C16" t="s">
+        <v>102</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
-        <v>45784</v>
+        <v>45855</v>
       </c>
       <c r="B17" t="s">
         <v>22</v>
       </c>
-      <c r="C17" t="s">
-        <v>96</v>
+      <c r="C17" s="5" t="s">
+        <v>100</v>
       </c>
       <c r="D17" t="s">
-        <v>97</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
-        <v>45725</v>
+        <v>45784</v>
       </c>
       <c r="B18" t="s">
         <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D18" t="s">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
-        <v>45696</v>
+        <v>45725</v>
       </c>
       <c r="B19" t="s">
         <v>22</v>
       </c>
       <c r="C19" t="s">
-        <v>93</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
+      </c>
+      <c r="D19" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
-        <v>45686</v>
+        <v>45696</v>
       </c>
       <c r="B20" t="s">
         <v>22</v>
       </c>
       <c r="C20" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
+        <v>45686</v>
+      </c>
+      <c r="B21" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" t="s">
+        <v>90</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="2">
         <v>45623</v>
       </c>
-      <c r="B21" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="B22" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" t="s">
         <v>89</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D22" t="s">
         <v>88</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A22" s="2">
-        <v>45584</v>
-      </c>
-      <c r="B22" t="s">
-        <v>22</v>
-      </c>
-      <c r="C22" t="s">
-        <v>87</v>
-      </c>
-      <c r="D22" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
-        <v>45568</v>
+        <v>45584</v>
       </c>
       <c r="B23" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="5" t="s">
-        <v>85</v>
+      <c r="C23" t="s">
+        <v>87</v>
       </c>
       <c r="D23" t="s">
-        <v>83</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
-        <v>45565</v>
+        <v>45568</v>
       </c>
       <c r="B24" t="s">
         <v>22</v>
       </c>
-      <c r="C24" t="s">
-        <v>82</v>
+      <c r="C24" s="5" t="s">
+        <v>85</v>
       </c>
       <c r="D24" t="s">
-        <v>81</v>
+        <v>83</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
-        <v>45557</v>
+        <v>45565</v>
       </c>
       <c r="B25" t="s">
         <v>22</v>
       </c>
       <c r="C25" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D25" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
-        <v>45537</v>
+        <v>45557</v>
       </c>
       <c r="B26" t="s">
         <v>22</v>
       </c>
       <c r="C26" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D26" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
-        <v>45533</v>
+        <v>45537</v>
       </c>
       <c r="B27" t="s">
         <v>22</v>
       </c>
       <c r="C27" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D27" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
-        <v>45509</v>
+        <v>45533</v>
       </c>
       <c r="B28" t="s">
         <v>22</v>
       </c>
       <c r="C28" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D28" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
-        <v>45504</v>
+        <v>45509</v>
       </c>
       <c r="B29" t="s">
         <v>22</v>
       </c>
       <c r="C29" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D29" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
-        <v>45490</v>
+        <v>45504</v>
       </c>
       <c r="B30" t="s">
         <v>22</v>
       </c>
       <c r="C30" t="s">
-        <v>69</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
+      </c>
+      <c r="D30" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
-        <v>45482</v>
+        <v>45490</v>
       </c>
       <c r="B31" t="s">
         <v>22</v>
       </c>
       <c r="C31" t="s">
-        <v>67</v>
-      </c>
-      <c r="D31" t="s">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
-        <v>45473</v>
+        <v>45482</v>
       </c>
       <c r="B32" t="s">
         <v>22</v>
       </c>
       <c r="C32" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D32" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
-        <v>45443</v>
+        <v>45473</v>
       </c>
       <c r="B33" t="s">
         <v>22</v>
       </c>
       <c r="C33" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D33" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
-        <v>45357</v>
+        <v>45443</v>
       </c>
       <c r="B34" t="s">
         <v>22</v>
       </c>
       <c r="C34" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D34" t="s">
-        <v>61</v>
-      </c>
-      <c r="E34" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
-        <v>45352</v>
+        <v>45357</v>
       </c>
       <c r="B35" t="s">
         <v>22</v>
       </c>
       <c r="C35" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D35" t="s">
-        <v>58</v>
+        <v>61</v>
+      </c>
+      <c r="E35" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
-        <v>45240</v>
+        <v>45352</v>
       </c>
       <c r="B36" t="s">
         <v>22</v>
       </c>
       <c r="C36" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D36" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
-        <v>45212</v>
+        <v>45240</v>
       </c>
       <c r="B37" t="s">
         <v>22</v>
       </c>
       <c r="C37" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D37" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
-        <v>45211</v>
-      </c>
-      <c r="B38" s="2" t="s">
+        <v>45212</v>
+      </c>
+      <c r="B38" t="s">
         <v>22</v>
       </c>
       <c r="C38" t="s">
-        <v>51</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
+      </c>
+      <c r="D38" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
-        <v>45147</v>
+        <v>45211</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C39" t="s">
-        <v>47</v>
-      </c>
-      <c r="D39" t="s">
-        <v>48</v>
-      </c>
-      <c r="E39" t="s">
-        <v>49</v>
+        <v>51</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
+        <v>45147</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C40" t="s">
+        <v>47</v>
+      </c>
+      <c r="D40" t="s">
+        <v>48</v>
+      </c>
+      <c r="E40" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A41" s="2">
         <v>45143</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C40" t="s">
+      <c r="B41" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" t="s">
         <v>44</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D41" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A41" s="2">
+    <row r="42" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A42" s="2">
         <v>45119</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C41" s="3" t="s">
+      <c r="B42" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C42" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D42" s="1" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A42" s="2">
-        <v>45113</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C42" t="s">
-        <v>26</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
-        <v>45112</v>
+        <v>45113</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C43" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
-        <v>45083</v>
+        <v>45112</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C44" t="s">
-        <v>12</v>
-      </c>
-      <c r="D44" t="s">
-        <v>3</v>
+        <v>28</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
-        <v>45082</v>
+        <v>45083</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C45" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D45" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
-        <v>45018</v>
+        <v>45082</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C46" t="s">
-        <v>54</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>55</v>
+        <v>13</v>
+      </c>
+      <c r="D46" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
-        <v>45014</v>
+        <v>45018</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C47" t="s">
-        <v>14</v>
-      </c>
-      <c r="D47" t="s">
-        <v>5</v>
+        <v>54</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
-        <v>44992</v>
+        <v>45014</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C48" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D48" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
-        <v>44959</v>
+        <v>44992</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C49" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D49" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
-        <v>44930</v>
+        <v>44959</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C50" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D50" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
-        <v>44897</v>
+        <v>44930</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C51" t="s">
-        <v>18</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
+      </c>
+      <c r="D51" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
-        <v>44682</v>
+        <v>44897</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C52" t="s">
-        <v>19</v>
-      </c>
-      <c r="D52" t="s">
-        <v>9</v>
+        <v>18</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" s="2">
-        <v>44601</v>
+        <v>44682</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C53" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D53" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
-        <v>44725</v>
+        <v>44601</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C54" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D54" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" s="2">
-        <v>44723</v>
+        <v>44725</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C55" t="s">
-        <v>42</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
+      </c>
+      <c r="D55" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
-        <v>44326</v>
+        <v>44723</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C56" t="s">
-        <v>38</v>
-      </c>
-      <c r="D56" t="s">
-        <v>39</v>
+        <v>42</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" s="2">
-        <v>44265</v>
+        <v>44326</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C57" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D57" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
-        <v>44148</v>
+        <v>44265</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C58" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D58" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" s="2">
-        <v>44146</v>
+        <v>44148</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C59" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D59" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
-        <v>44144</v>
+        <v>44146</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C60" t="s">
+        <v>32</v>
+      </c>
+      <c r="D60" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61" s="2">
+        <v>44144</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C61" t="s">
         <v>31</v>
       </c>
-      <c r="D60" t="s">
+      <c r="D61" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B61" s="2"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B62" s="2"/>
     </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B63" s="2"/>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A31:D51">
-    <sortCondition ref="B31:B51"/>
-    <sortCondition descending="1" ref="A31:A51"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A32:D52">
+    <sortCondition ref="B32:B52"/>
+    <sortCondition descending="1" ref="A32:A52"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="D51" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="D41" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="D42" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="D43" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="D55" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="D38" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="D46" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="D30" r:id="rId8" xr:uid="{FA3531C4-3B8B-4257-B20B-BB3BF511A818}"/>
-    <hyperlink ref="E23" r:id="rId9" xr:uid="{461EAE59-6B89-4B06-BC7F-5D62D70EDCD6}"/>
-    <hyperlink ref="D20" r:id="rId10" xr:uid="{9FC614FC-A94D-4784-8E8F-DFD619EA88C0}"/>
-    <hyperlink ref="D19" r:id="rId11" xr:uid="{0B29772C-F7FE-40CC-A257-2848F4518174}"/>
-    <hyperlink ref="E17" r:id="rId12" xr:uid="{C474B74F-3E03-433F-BC35-18768486A4FB}"/>
-    <hyperlink ref="E16" r:id="rId13" xr:uid="{209BE10C-36A4-4475-BDA6-365C34A7A7B4}"/>
-    <hyperlink ref="D15" r:id="rId14" xr:uid="{D908A389-6872-41E0-B81F-166FB55D55A3}"/>
-    <hyperlink ref="D14" r:id="rId15" xr:uid="{1BBDB9F5-EA33-4B8D-A13B-752105B1611A}"/>
+    <hyperlink ref="D52" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="D42" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="D43" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="D44" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="D56" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="D39" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="D47" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="D31" r:id="rId8" xr:uid="{FA3531C4-3B8B-4257-B20B-BB3BF511A818}"/>
+    <hyperlink ref="E24" r:id="rId9" xr:uid="{461EAE59-6B89-4B06-BC7F-5D62D70EDCD6}"/>
+    <hyperlink ref="D21" r:id="rId10" xr:uid="{9FC614FC-A94D-4784-8E8F-DFD619EA88C0}"/>
+    <hyperlink ref="D20" r:id="rId11" xr:uid="{0B29772C-F7FE-40CC-A257-2848F4518174}"/>
+    <hyperlink ref="E18" r:id="rId12" xr:uid="{C474B74F-3E03-433F-BC35-18768486A4FB}"/>
+    <hyperlink ref="E17" r:id="rId13" xr:uid="{209BE10C-36A4-4475-BDA6-365C34A7A7B4}"/>
+    <hyperlink ref="D16" r:id="rId14" xr:uid="{D908A389-6872-41E0-B81F-166FB55D55A3}"/>
+    <hyperlink ref="D15" r:id="rId15" xr:uid="{1BBDB9F5-EA33-4B8D-A13B-752105B1611A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId16"/>

--- a/data/posts.xlsx
+++ b/data/posts.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53ACF88F-A373-4C10-8E33-3DAE1FC87037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B7261EF-A8FF-4BFD-A37D-797E89D3E66C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18030" yWindow="260" windowWidth="19930" windowHeight="20890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -69,33 +69,6 @@
     <t>https://www.linkedin.com/pulse/regulators-board-estimands-kaspar-rufibach/</t>
   </si>
   <si>
-    <t xml:space="preserve"> Why can't we simply get rid of RCTs?</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Why do we randomize in RCTs?</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Quantification of follow-up</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> How can the estimands addendum framework be “married” with competing risks?</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Trial design using multistate modelling for PFS and OS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Estimation of AE risk in RCTs</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Are regulators on board with estimands?</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Thoughts on my 10th year anniversary at Roche</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Academia - Industry collaboration award of Ulm University for Roche's long-term collaboration with Jan Beyersmann</t>
-  </si>
-  <si>
     <t>type</t>
   </si>
   <si>
@@ -424,6 +397,33 @@
   </si>
   <si>
     <t>https://www.linkedin.com/posts/kasparrufibach_biostatistics-inference-clinicaltrials-share-7457711254632079362-rNIo?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAAQJ2qsB_r_XsYhAPWyf_WQeC5V6NOcbIXo</t>
+  </si>
+  <si>
+    <t>Why do we randomize in RCTs?</t>
+  </si>
+  <si>
+    <t>Why can't we simply get rid of RCTs?</t>
+  </si>
+  <si>
+    <t>Quantification of follow-up</t>
+  </si>
+  <si>
+    <t>How can the estimands addendum framework be “married” with competing risks?</t>
+  </si>
+  <si>
+    <t>Trial design using multistate modelling for PFS and OS</t>
+  </si>
+  <si>
+    <t>Estimation of AE risk in RCTs</t>
+  </si>
+  <si>
+    <t>Are regulators on board with estimands?</t>
+  </si>
+  <si>
+    <t>Thoughts on my 10th year anniversary at Roche</t>
+  </si>
+  <si>
+    <t>Academia - Industry collaboration award of Ulm University for Roche's long-term collaboration with Jan Beyersmann</t>
   </si>
 </sst>
 </file>
@@ -781,7 +781,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -790,7 +790,7 @@
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -798,13 +798,13 @@
         <v>46148</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="D2" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -812,13 +812,13 @@
         <v>46145</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="D3" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -826,13 +826,13 @@
         <v>46084</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="D4" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -840,13 +840,13 @@
         <v>46030</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="D5" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -854,13 +854,13 @@
         <v>46001</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="D6" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -868,13 +868,13 @@
         <v>45992</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="D7" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -882,13 +882,13 @@
         <v>45989</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -896,13 +896,13 @@
         <v>45964</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="D9" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -910,13 +910,13 @@
         <v>45964</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="D10" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -924,13 +924,13 @@
         <v>45959</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="D11" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -938,13 +938,13 @@
         <v>45956</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="D12" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -952,13 +952,13 @@
         <v>45941</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="D13" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -966,13 +966,13 @@
         <v>45927</v>
       </c>
       <c r="B14" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="D14" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -980,13 +980,13 @@
         <v>45871</v>
       </c>
       <c r="B15" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -994,13 +994,13 @@
         <v>45868</v>
       </c>
       <c r="B16" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C16" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -1008,16 +1008,16 @@
         <v>45855</v>
       </c>
       <c r="B17" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="D17" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -1025,16 +1025,16 @@
         <v>45784</v>
       </c>
       <c r="B18" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C18" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="D18" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -1042,13 +1042,13 @@
         <v>45725</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C19" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="D19" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -1056,13 +1056,13 @@
         <v>45696</v>
       </c>
       <c r="B20" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C20" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -1070,13 +1070,13 @@
         <v>45686</v>
       </c>
       <c r="B21" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C21" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -1084,13 +1084,13 @@
         <v>45623</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C22" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D22" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
@@ -1098,13 +1098,13 @@
         <v>45584</v>
       </c>
       <c r="B23" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C23" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="D23" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
@@ -1112,16 +1112,16 @@
         <v>45568</v>
       </c>
       <c r="B24" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="D24" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
@@ -1129,13 +1129,13 @@
         <v>45565</v>
       </c>
       <c r="B25" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C25" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="D25" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
@@ -1143,13 +1143,13 @@
         <v>45557</v>
       </c>
       <c r="B26" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C26" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="D26" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
@@ -1157,13 +1157,13 @@
         <v>45537</v>
       </c>
       <c r="B27" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C27" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D27" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
@@ -1171,13 +1171,13 @@
         <v>45533</v>
       </c>
       <c r="B28" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C28" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D28" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
@@ -1185,13 +1185,13 @@
         <v>45509</v>
       </c>
       <c r="B29" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C29" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="D29" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
@@ -1199,13 +1199,13 @@
         <v>45504</v>
       </c>
       <c r="B30" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C30" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D30" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
@@ -1213,13 +1213,13 @@
         <v>45490</v>
       </c>
       <c r="B31" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C31" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
@@ -1227,13 +1227,13 @@
         <v>45482</v>
       </c>
       <c r="B32" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C32" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D32" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
@@ -1241,13 +1241,13 @@
         <v>45473</v>
       </c>
       <c r="B33" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C33" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="D33" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
@@ -1255,13 +1255,13 @@
         <v>45443</v>
       </c>
       <c r="B34" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C34" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="D34" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
@@ -1269,16 +1269,16 @@
         <v>45357</v>
       </c>
       <c r="B35" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C35" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="D35" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="E35" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
@@ -1286,13 +1286,13 @@
         <v>45352</v>
       </c>
       <c r="B36" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C36" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="D36" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
@@ -1300,13 +1300,13 @@
         <v>45240</v>
       </c>
       <c r="B37" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C37" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="D37" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
@@ -1314,13 +1314,13 @@
         <v>45212</v>
       </c>
       <c r="B38" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C38" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D38" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
@@ -1328,13 +1328,13 @@
         <v>45211</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C39" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
@@ -1342,16 +1342,16 @@
         <v>45147</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C40" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="D40" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E40" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
@@ -1359,13 +1359,13 @@
         <v>45143</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C41" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="D41" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
@@ -1373,13 +1373,13 @@
         <v>45119</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
@@ -1387,13 +1387,13 @@
         <v>45113</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C43" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
@@ -1401,13 +1401,13 @@
         <v>45112</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C44" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
@@ -1415,10 +1415,10 @@
         <v>45083</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C45" t="s">
-        <v>12</v>
+        <v>123</v>
       </c>
       <c r="D45" t="s">
         <v>3</v>
@@ -1429,10 +1429,10 @@
         <v>45082</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C46" t="s">
-        <v>13</v>
+        <v>122</v>
       </c>
       <c r="D46" t="s">
         <v>4</v>
@@ -1443,13 +1443,13 @@
         <v>45018</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C47" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
@@ -1457,10 +1457,10 @@
         <v>45014</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C48" t="s">
-        <v>14</v>
+        <v>124</v>
       </c>
       <c r="D48" t="s">
         <v>5</v>
@@ -1471,10 +1471,10 @@
         <v>44992</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C49" t="s">
-        <v>15</v>
+        <v>125</v>
       </c>
       <c r="D49" t="s">
         <v>6</v>
@@ -1485,10 +1485,10 @@
         <v>44959</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C50" t="s">
-        <v>16</v>
+        <v>126</v>
       </c>
       <c r="D50" t="s">
         <v>7</v>
@@ -1499,10 +1499,10 @@
         <v>44930</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C51" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="D51" t="s">
         <v>8</v>
@@ -1513,10 +1513,10 @@
         <v>44897</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C52" t="s">
-        <v>18</v>
+        <v>128</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>11</v>
@@ -1527,10 +1527,10 @@
         <v>44682</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C53" t="s">
-        <v>19</v>
+        <v>129</v>
       </c>
       <c r="D53" t="s">
         <v>9</v>
@@ -1541,10 +1541,10 @@
         <v>44601</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C54" t="s">
-        <v>20</v>
+        <v>130</v>
       </c>
       <c r="D54" t="s">
         <v>10</v>
@@ -1555,13 +1555,13 @@
         <v>44725</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C55" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="D55" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
@@ -1569,13 +1569,13 @@
         <v>44723</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C56" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
@@ -1583,13 +1583,13 @@
         <v>44326</v>
       </c>
       <c r="B57" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C57" t="s">
+        <v>29</v>
+      </c>
+      <c r="D57" t="s">
         <v>30</v>
-      </c>
-      <c r="C57" t="s">
-        <v>38</v>
-      </c>
-      <c r="D57" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
@@ -1597,13 +1597,13 @@
         <v>44265</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C58" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D58" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
@@ -1611,13 +1611,13 @@
         <v>44148</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C59" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D59" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
@@ -1625,13 +1625,13 @@
         <v>44146</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C60" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D60" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
@@ -1639,13 +1639,13 @@
         <v>44144</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C61" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D61" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">

--- a/data/posts.xlsx
+++ b/data/posts.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B7261EF-A8FF-4BFD-A37D-797E89D3E66C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7B3B14F-0BC2-4145-8A43-5186EB53BCBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18030" yWindow="260" windowWidth="19930" windowHeight="20890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="133">
   <si>
     <t>date</t>
   </si>
@@ -424,6 +424,12 @@
   </si>
   <si>
     <t>Academia - Industry collaboration award of Ulm University for Roche's long-term collaboration with Jan Beyersmann</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/posts/kasparrufibach_biostatistics-clinical-share-7461010236905046016-NMUX?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAAQJ2qsB_r_XsYhAPWyf_WQeC5V6NOcbIXo</t>
+  </si>
+  <si>
+    <t>Uncertainty when stopping at an interim is proportional to absolute information</t>
   </si>
 </sst>
 </file>
@@ -766,17 +772,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E63"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:E64"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="106.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="106.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="223" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="99.453125" customWidth="1"/>
+    <col min="5" max="5" width="99.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -793,119 +799,119 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
+        <v>46157</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
         <v>46148</v>
       </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
         <v>120</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D3" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="2">
+    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
         <v>46145</v>
       </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
         <v>119</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D4" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="2">
+    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
         <v>46084</v>
       </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
         <v>116</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D5" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="2">
+    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
         <v>46030</v>
       </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
         <v>114</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D6" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="2">
+    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
         <v>46001</v>
       </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
         <v>113</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D7" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="2">
+    <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
         <v>45992</v>
       </c>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
         <v>109</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D8" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="2">
+    <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
         <v>45989</v>
       </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" t="s">
         <v>108</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="2">
-        <v>45964</v>
-      </c>
-      <c r="B9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" t="s">
-        <v>104</v>
-      </c>
-      <c r="D9" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>45964</v>
       </c>
@@ -913,768 +919,782 @@
         <v>13</v>
       </c>
       <c r="C10" t="s">
+        <v>104</v>
+      </c>
+      <c r="D10" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>45964</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" t="s">
         <v>103</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D11" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="2">
+    <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
         <v>45959</v>
       </c>
-      <c r="B11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="B12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" t="s">
         <v>107</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D12" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="2">
+    <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
         <v>45956</v>
       </c>
-      <c r="B12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="B13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" t="s">
         <v>100</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D13" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="2">
+    <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
         <v>45941</v>
       </c>
-      <c r="B13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="B14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" t="s">
         <v>98</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D14" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="2">
+    <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
         <v>45927</v>
       </c>
-      <c r="B14" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="B15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" t="s">
         <v>97</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D15" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="2">
+    <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
         <v>45871</v>
       </c>
-      <c r="B15" t="s">
-        <v>13</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="B16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" t="s">
         <v>94</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D16" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="2">
+    <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
         <v>45868</v>
       </c>
-      <c r="B16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="B17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" t="s">
         <v>93</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D17" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="2">
+    <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
         <v>45855</v>
       </c>
-      <c r="B17" t="s">
-        <v>13</v>
-      </c>
-      <c r="C17" s="5" t="s">
+      <c r="B18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D18" t="s">
         <v>90</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E18" s="4" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="2">
+    <row r="19" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
         <v>45784</v>
       </c>
-      <c r="B18" t="s">
-        <v>13</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="B19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" t="s">
         <v>87</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D19" t="s">
         <v>88</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E19" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="2">
+    <row r="20" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
         <v>45725</v>
       </c>
-      <c r="B19" t="s">
-        <v>13</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="B20" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" t="s">
         <v>85</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D20" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="2">
+    <row r="21" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
         <v>45696</v>
       </c>
-      <c r="B20" t="s">
-        <v>13</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="B21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" t="s">
         <v>84</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D21" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="2">
+    <row r="22" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
         <v>45686</v>
       </c>
-      <c r="B21" t="s">
-        <v>13</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="B22" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" t="s">
         <v>81</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="2">
+    <row r="23" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
         <v>45623</v>
       </c>
-      <c r="B22" t="s">
-        <v>13</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="B23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" t="s">
         <v>80</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D23" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A23" s="2">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
         <v>45584</v>
       </c>
-      <c r="B23" t="s">
-        <v>13</v>
-      </c>
-      <c r="C23" t="s">
+      <c r="B24" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" t="s">
         <v>78</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D24" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A24" s="2">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
         <v>45568</v>
       </c>
-      <c r="B24" t="s">
-        <v>13</v>
-      </c>
-      <c r="C24" s="5" t="s">
+      <c r="B25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D25" t="s">
         <v>74</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E25" s="4" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A25" s="2">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
         <v>45565</v>
       </c>
-      <c r="B25" t="s">
-        <v>13</v>
-      </c>
-      <c r="C25" t="s">
+      <c r="B26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" t="s">
         <v>73</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D26" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A26" s="2">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
         <v>45557</v>
       </c>
-      <c r="B26" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" t="s">
+      <c r="B27" t="s">
+        <v>13</v>
+      </c>
+      <c r="C27" t="s">
         <v>70</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D27" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A27" s="2">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
         <v>45537</v>
       </c>
-      <c r="B27" t="s">
-        <v>13</v>
-      </c>
-      <c r="C27" t="s">
+      <c r="B28" t="s">
+        <v>13</v>
+      </c>
+      <c r="C28" t="s">
         <v>68</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D28" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A28" s="2">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
         <v>45533</v>
       </c>
-      <c r="B28" t="s">
-        <v>13</v>
-      </c>
-      <c r="C28" t="s">
+      <c r="B29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" t="s">
         <v>66</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D29" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A29" s="2">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
         <v>45509</v>
       </c>
-      <c r="B29" t="s">
-        <v>13</v>
-      </c>
-      <c r="C29" t="s">
+      <c r="B30" t="s">
+        <v>13</v>
+      </c>
+      <c r="C30" t="s">
         <v>62</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D30" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A30" s="2">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
         <v>45504</v>
       </c>
-      <c r="B30" t="s">
-        <v>13</v>
-      </c>
-      <c r="C30" t="s">
+      <c r="B31" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" t="s">
         <v>64</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D31" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A31" s="2">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
         <v>45490</v>
       </c>
-      <c r="B31" t="s">
-        <v>13</v>
-      </c>
-      <c r="C31" t="s">
+      <c r="B32" t="s">
+        <v>13</v>
+      </c>
+      <c r="C32" t="s">
         <v>60</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D32" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A32" s="2">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
         <v>45482</v>
       </c>
-      <c r="B32" t="s">
-        <v>13</v>
-      </c>
-      <c r="C32" t="s">
+      <c r="B33" t="s">
+        <v>13</v>
+      </c>
+      <c r="C33" t="s">
         <v>58</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D33" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A33" s="2">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
         <v>45473</v>
       </c>
-      <c r="B33" t="s">
-        <v>13</v>
-      </c>
-      <c r="C33" t="s">
+      <c r="B34" t="s">
+        <v>13</v>
+      </c>
+      <c r="C34" t="s">
         <v>56</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D34" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A34" s="2">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
         <v>45443</v>
       </c>
-      <c r="B34" t="s">
-        <v>13</v>
-      </c>
-      <c r="C34" t="s">
+      <c r="B35" t="s">
+        <v>13</v>
+      </c>
+      <c r="C35" t="s">
         <v>54</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D35" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A35" s="2">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
         <v>45357</v>
       </c>
-      <c r="B35" t="s">
-        <v>13</v>
-      </c>
-      <c r="C35" t="s">
+      <c r="B36" t="s">
+        <v>13</v>
+      </c>
+      <c r="C36" t="s">
         <v>51</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D36" t="s">
         <v>52</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E36" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A36" s="2">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
         <v>45352</v>
       </c>
-      <c r="B36" t="s">
-        <v>13</v>
-      </c>
-      <c r="C36" t="s">
+      <c r="B37" t="s">
+        <v>13</v>
+      </c>
+      <c r="C37" t="s">
         <v>50</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D37" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A37" s="2">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
         <v>45240</v>
       </c>
-      <c r="B37" t="s">
-        <v>13</v>
-      </c>
-      <c r="C37" t="s">
+      <c r="B38" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" t="s">
         <v>48</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D38" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A38" s="2">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="2">
         <v>45212</v>
       </c>
-      <c r="B38" t="s">
-        <v>13</v>
-      </c>
-      <c r="C38" t="s">
+      <c r="B39" t="s">
+        <v>13</v>
+      </c>
+      <c r="C39" t="s">
         <v>44</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D39" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A39" s="2">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
         <v>45211</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C39" t="s">
+      <c r="B40" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C40" t="s">
         <v>42</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="D40" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A40" s="2">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="2">
         <v>45147</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C40" t="s">
+      <c r="B41" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C41" t="s">
         <v>38</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D41" t="s">
         <v>39</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E41" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A41" s="2">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
         <v>45143</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C41" t="s">
+      <c r="B42" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C42" t="s">
         <v>35</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D42" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A42" s="2">
+    <row r="43" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A43" s="2">
         <v>45119</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C42" s="3" t="s">
+      <c r="B43" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C43" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="D43" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A43" s="2">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
         <v>45113</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C43" t="s">
+      <c r="B44" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C44" t="s">
         <v>17</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="D44" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A44" s="2">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="2">
         <v>45112</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C44" t="s">
+      <c r="B45" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C45" t="s">
         <v>19</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="D45" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A45" s="2">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="2">
         <v>45083</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C45" t="s">
+      <c r="B46" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C46" t="s">
         <v>123</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D46" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A46" s="2">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="2">
         <v>45082</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C46" t="s">
+      <c r="B47" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C47" t="s">
         <v>122</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D47" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A47" s="2">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="2">
         <v>45018</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C47" t="s">
+      <c r="B48" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C48" t="s">
         <v>45</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="D48" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A48" s="2">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="2">
         <v>45014</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C48" t="s">
+      <c r="B49" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C49" t="s">
         <v>124</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D49" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" s="2">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="2">
         <v>44992</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C49" t="s">
+      <c r="B50" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50" t="s">
         <v>125</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D50" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" s="2">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="2">
         <v>44959</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C50" t="s">
+      <c r="B51" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C51" t="s">
         <v>126</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D51" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" s="2">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="2">
         <v>44930</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C51" t="s">
+      <c r="B52" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C52" t="s">
         <v>127</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D52" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" s="2">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="2">
         <v>44897</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C52" t="s">
+      <c r="B53" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C53" t="s">
         <v>128</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="D53" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" s="2">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="2">
         <v>44682</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C53" t="s">
+      <c r="B54" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C54" t="s">
         <v>129</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D54" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54" s="2">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="2">
         <v>44601</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C54" t="s">
+      <c r="B55" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C55" t="s">
         <v>130</v>
       </c>
-      <c r="D54" t="s">
+      <c r="D55" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A55" s="2">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="2">
         <v>44725</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C55" t="s">
-        <v>31</v>
-      </c>
-      <c r="D55" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A56" s="2">
-        <v>44723</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C56" t="s">
-        <v>33</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+      <c r="D56" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
-        <v>44326</v>
+        <v>44723</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C57" t="s">
-        <v>29</v>
-      </c>
-      <c r="D57" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
-        <v>44265</v>
+        <v>44326</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C58" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D58" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
-        <v>44148</v>
+        <v>44265</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C59" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D59" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
-        <v>44146</v>
+        <v>44148</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C60" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D60" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
-        <v>44144</v>
+        <v>44146</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C61" t="s">
+        <v>23</v>
+      </c>
+      <c r="D61" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="2">
+        <v>44144</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C62" t="s">
         <v>22</v>
       </c>
-      <c r="D61" t="s">
+      <c r="D62" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B62" s="2"/>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B63" s="2"/>
     </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B64" s="2"/>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A32:D52">
-    <sortCondition ref="B32:B52"/>
-    <sortCondition descending="1" ref="A32:A52"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A33:D53">
+    <sortCondition ref="B33:B53"/>
+    <sortCondition descending="1" ref="A33:A53"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="D52" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="D42" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="D43" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="D44" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="D56" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="D39" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="D47" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="D31" r:id="rId8" xr:uid="{FA3531C4-3B8B-4257-B20B-BB3BF511A818}"/>
-    <hyperlink ref="E24" r:id="rId9" xr:uid="{461EAE59-6B89-4B06-BC7F-5D62D70EDCD6}"/>
-    <hyperlink ref="D21" r:id="rId10" xr:uid="{9FC614FC-A94D-4784-8E8F-DFD619EA88C0}"/>
-    <hyperlink ref="D20" r:id="rId11" xr:uid="{0B29772C-F7FE-40CC-A257-2848F4518174}"/>
-    <hyperlink ref="E18" r:id="rId12" xr:uid="{C474B74F-3E03-433F-BC35-18768486A4FB}"/>
-    <hyperlink ref="E17" r:id="rId13" xr:uid="{209BE10C-36A4-4475-BDA6-365C34A7A7B4}"/>
-    <hyperlink ref="D16" r:id="rId14" xr:uid="{D908A389-6872-41E0-B81F-166FB55D55A3}"/>
-    <hyperlink ref="D15" r:id="rId15" xr:uid="{1BBDB9F5-EA33-4B8D-A13B-752105B1611A}"/>
+    <hyperlink ref="D53" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="D43" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="D44" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="D45" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="D57" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="D40" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="D48" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="D32" r:id="rId8" xr:uid="{FA3531C4-3B8B-4257-B20B-BB3BF511A818}"/>
+    <hyperlink ref="E25" r:id="rId9" xr:uid="{461EAE59-6B89-4B06-BC7F-5D62D70EDCD6}"/>
+    <hyperlink ref="D22" r:id="rId10" xr:uid="{9FC614FC-A94D-4784-8E8F-DFD619EA88C0}"/>
+    <hyperlink ref="D21" r:id="rId11" xr:uid="{0B29772C-F7FE-40CC-A257-2848F4518174}"/>
+    <hyperlink ref="E19" r:id="rId12" xr:uid="{C474B74F-3E03-433F-BC35-18768486A4FB}"/>
+    <hyperlink ref="E18" r:id="rId13" xr:uid="{209BE10C-36A4-4475-BDA6-365C34A7A7B4}"/>
+    <hyperlink ref="D17" r:id="rId14" xr:uid="{D908A389-6872-41E0-B81F-166FB55D55A3}"/>
+    <hyperlink ref="D16" r:id="rId15" xr:uid="{1BBDB9F5-EA33-4B8D-A13B-752105B1611A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId16"/>

--- a/data/posts.xlsx
+++ b/data/posts.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7B3B14F-0BC2-4145-8A43-5186EB53BCBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1E243A0-8538-4AA1-AC32-67076F5499D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="135">
   <si>
     <t>date</t>
   </si>
@@ -430,6 +430,12 @@
   </si>
   <si>
     <t>Uncertainty when stopping at an interim is proportional to absolute information</t>
+  </si>
+  <si>
+    <t>Why do a PhD?</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/posts/kasparrufibach_phd-statistics-mathematics-ugcPost-7462018304820428800-dPBW?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAAQJ2qsB_r_XsYhAPWyf_WQeC5V6NOcbIXo</t>
   </si>
 </sst>
 </file>
@@ -772,7 +778,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E64"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -801,128 +807,128 @@
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
-        <v>46157</v>
+        <v>46191</v>
       </c>
       <c r="B2" t="s">
         <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
-        <v>46148</v>
+        <v>46157</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="D3" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
-        <v>46145</v>
+        <v>46148</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D4" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
-        <v>46084</v>
+        <v>46145</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>46030</v>
+        <v>46084</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <v>46001</v>
+        <v>46030</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D7" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>45992</v>
+        <v>46001</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>108</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
+      </c>
+      <c r="D9" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>45964</v>
+        <v>45989</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>104</v>
-      </c>
-      <c r="D10" t="s">
-        <v>105</v>
+        <v>108</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -933,768 +939,782 @@
         <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D11" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
-        <v>45959</v>
+        <v>45964</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D12" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
-        <v>45956</v>
+        <v>45959</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="D13" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <v>45941</v>
+        <v>45956</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D14" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
-        <v>45927</v>
+        <v>45941</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D15" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
-        <v>45871</v>
+        <v>45927</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
       </c>
       <c r="C16" t="s">
-        <v>94</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="D16" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
-        <v>45868</v>
+        <v>45871</v>
       </c>
       <c r="B17" t="s">
         <v>13</v>
       </c>
       <c r="C17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
-        <v>45855</v>
+        <v>45868</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="D18" t="s">
-        <v>90</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>75</v>
+      <c r="C18" t="s">
+        <v>93</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
-        <v>45784</v>
+        <v>45855</v>
       </c>
       <c r="B19" t="s">
         <v>13</v>
       </c>
-      <c r="C19" t="s">
-        <v>87</v>
+      <c r="C19" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="D19" t="s">
-        <v>88</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
-        <v>45725</v>
+        <v>45784</v>
       </c>
       <c r="B20" t="s">
         <v>13</v>
       </c>
       <c r="C20" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D20" t="s">
-        <v>86</v>
+        <v>88</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
-        <v>45696</v>
+        <v>45725</v>
       </c>
       <c r="B21" t="s">
         <v>13</v>
       </c>
       <c r="C21" t="s">
-        <v>84</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
+      </c>
+      <c r="D21" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
-        <v>45686</v>
+        <v>45696</v>
       </c>
       <c r="B22" t="s">
         <v>13</v>
       </c>
       <c r="C22" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
+        <v>45686</v>
+      </c>
+      <c r="B23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" t="s">
+        <v>81</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
         <v>45623</v>
       </c>
-      <c r="B23" t="s">
-        <v>13</v>
-      </c>
-      <c r="C23" t="s">
+      <c r="B24" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" t="s">
         <v>80</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D24" t="s">
         <v>79</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="2">
-        <v>45584</v>
-      </c>
-      <c r="B24" t="s">
-        <v>13</v>
-      </c>
-      <c r="C24" t="s">
-        <v>78</v>
-      </c>
-      <c r="D24" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
-        <v>45568</v>
+        <v>45584</v>
       </c>
       <c r="B25" t="s">
         <v>13</v>
       </c>
-      <c r="C25" s="5" t="s">
-        <v>76</v>
+      <c r="C25" t="s">
+        <v>78</v>
       </c>
       <c r="D25" t="s">
-        <v>74</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
-        <v>45565</v>
+        <v>45568</v>
       </c>
       <c r="B26" t="s">
         <v>13</v>
       </c>
-      <c r="C26" t="s">
-        <v>73</v>
+      <c r="C26" s="5" t="s">
+        <v>76</v>
       </c>
       <c r="D26" t="s">
-        <v>72</v>
+        <v>74</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
-        <v>45557</v>
+        <v>45565</v>
       </c>
       <c r="B27" t="s">
         <v>13</v>
       </c>
       <c r="C27" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D27" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
-        <v>45537</v>
+        <v>45557</v>
       </c>
       <c r="B28" t="s">
         <v>13</v>
       </c>
       <c r="C28" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D28" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
-        <v>45533</v>
+        <v>45537</v>
       </c>
       <c r="B29" t="s">
         <v>13</v>
       </c>
       <c r="C29" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D29" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
-        <v>45509</v>
+        <v>45533</v>
       </c>
       <c r="B30" t="s">
         <v>13</v>
       </c>
       <c r="C30" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D30" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
-        <v>45504</v>
+        <v>45509</v>
       </c>
       <c r="B31" t="s">
         <v>13</v>
       </c>
       <c r="C31" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D31" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
-        <v>45490</v>
+        <v>45504</v>
       </c>
       <c r="B32" t="s">
         <v>13</v>
       </c>
       <c r="C32" t="s">
-        <v>60</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
+      </c>
+      <c r="D32" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
-        <v>45482</v>
+        <v>45490</v>
       </c>
       <c r="B33" t="s">
         <v>13</v>
       </c>
       <c r="C33" t="s">
-        <v>58</v>
-      </c>
-      <c r="D33" t="s">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
-        <v>45473</v>
+        <v>45482</v>
       </c>
       <c r="B34" t="s">
         <v>13</v>
       </c>
       <c r="C34" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D34" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
-        <v>45443</v>
+        <v>45473</v>
       </c>
       <c r="B35" t="s">
         <v>13</v>
       </c>
       <c r="C35" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D35" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
-        <v>45357</v>
+        <v>45443</v>
       </c>
       <c r="B36" t="s">
         <v>13</v>
       </c>
       <c r="C36" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D36" t="s">
-        <v>52</v>
-      </c>
-      <c r="E36" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
-        <v>45352</v>
+        <v>45357</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
       </c>
       <c r="C37" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D37" t="s">
-        <v>49</v>
+        <v>52</v>
+      </c>
+      <c r="E37" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
-        <v>45240</v>
+        <v>45352</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
       </c>
       <c r="C38" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D38" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
-        <v>45212</v>
+        <v>45240</v>
       </c>
       <c r="B39" t="s">
         <v>13</v>
       </c>
       <c r="C39" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D39" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
-        <v>45211</v>
-      </c>
-      <c r="B40" s="2" t="s">
+        <v>45212</v>
+      </c>
+      <c r="B40" t="s">
         <v>13</v>
       </c>
       <c r="C40" t="s">
-        <v>42</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
+      </c>
+      <c r="D40" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
-        <v>45147</v>
+        <v>45211</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C41" t="s">
-        <v>38</v>
-      </c>
-      <c r="D41" t="s">
-        <v>39</v>
-      </c>
-      <c r="E41" t="s">
-        <v>40</v>
+        <v>42</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
+        <v>45147</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C42" t="s">
+        <v>38</v>
+      </c>
+      <c r="D42" t="s">
+        <v>39</v>
+      </c>
+      <c r="E42" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="2">
         <v>45143</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C42" t="s">
+      <c r="B43" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C43" t="s">
         <v>35</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D43" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A43" s="2">
+    <row r="44" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A44" s="2">
         <v>45119</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C43" s="3" t="s">
+      <c r="B44" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="D44" s="1" t="s">
         <v>14</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="2">
-        <v>45113</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C44" t="s">
-        <v>17</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
-        <v>45112</v>
+        <v>45113</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C45" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
-        <v>45083</v>
+        <v>45112</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C46" t="s">
-        <v>123</v>
-      </c>
-      <c r="D46" t="s">
-        <v>3</v>
+        <v>19</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
-        <v>45082</v>
+        <v>45083</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C47" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D47" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
-        <v>45018</v>
+        <v>45082</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C48" t="s">
-        <v>45</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>46</v>
+        <v>122</v>
+      </c>
+      <c r="D48" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
-        <v>45014</v>
+        <v>45018</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C49" t="s">
-        <v>124</v>
-      </c>
-      <c r="D49" t="s">
-        <v>5</v>
+        <v>45</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
-        <v>44992</v>
+        <v>45014</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D50" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
-        <v>44959</v>
+        <v>44992</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C51" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D51" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
-        <v>44930</v>
+        <v>44959</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C52" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D52" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
-        <v>44897</v>
+        <v>44930</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C53" t="s">
-        <v>128</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>11</v>
+        <v>127</v>
+      </c>
+      <c r="D53" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
-        <v>44682</v>
+        <v>44897</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C54" t="s">
-        <v>129</v>
-      </c>
-      <c r="D54" t="s">
-        <v>9</v>
+        <v>128</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
-        <v>44601</v>
+        <v>44682</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C55" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D55" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
-        <v>44725</v>
+        <v>44601</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C56" t="s">
-        <v>31</v>
+        <v>130</v>
       </c>
       <c r="D56" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
-        <v>44723</v>
+        <v>44725</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C57" t="s">
-        <v>33</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
+      </c>
+      <c r="D57" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
-        <v>44326</v>
+        <v>44723</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C58" t="s">
-        <v>29</v>
-      </c>
-      <c r="D58" t="s">
-        <v>30</v>
+        <v>33</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
-        <v>44265</v>
+        <v>44326</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C59" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D59" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
-        <v>44148</v>
+        <v>44265</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C60" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D60" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
-        <v>44146</v>
+        <v>44148</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C61" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D61" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
-        <v>44144</v>
+        <v>44146</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C62" t="s">
+        <v>23</v>
+      </c>
+      <c r="D62" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="2">
+        <v>44144</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C63" t="s">
         <v>22</v>
       </c>
-      <c r="D62" t="s">
+      <c r="D63" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B63" s="2"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B64" s="2"/>
     </row>
+    <row r="65" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B65" s="2"/>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A33:D53">
-    <sortCondition ref="B33:B53"/>
-    <sortCondition descending="1" ref="A33:A53"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A34:D54">
+    <sortCondition ref="B34:B54"/>
+    <sortCondition descending="1" ref="A34:A54"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="D53" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="D43" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="D44" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="D45" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="D57" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="D40" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="D48" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="D32" r:id="rId8" xr:uid="{FA3531C4-3B8B-4257-B20B-BB3BF511A818}"/>
-    <hyperlink ref="E25" r:id="rId9" xr:uid="{461EAE59-6B89-4B06-BC7F-5D62D70EDCD6}"/>
-    <hyperlink ref="D22" r:id="rId10" xr:uid="{9FC614FC-A94D-4784-8E8F-DFD619EA88C0}"/>
-    <hyperlink ref="D21" r:id="rId11" xr:uid="{0B29772C-F7FE-40CC-A257-2848F4518174}"/>
-    <hyperlink ref="E19" r:id="rId12" xr:uid="{C474B74F-3E03-433F-BC35-18768486A4FB}"/>
-    <hyperlink ref="E18" r:id="rId13" xr:uid="{209BE10C-36A4-4475-BDA6-365C34A7A7B4}"/>
-    <hyperlink ref="D17" r:id="rId14" xr:uid="{D908A389-6872-41E0-B81F-166FB55D55A3}"/>
-    <hyperlink ref="D16" r:id="rId15" xr:uid="{1BBDB9F5-EA33-4B8D-A13B-752105B1611A}"/>
+    <hyperlink ref="D54" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="D44" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="D45" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="D46" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="D58" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="D41" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="D49" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="D33" r:id="rId8" xr:uid="{FA3531C4-3B8B-4257-B20B-BB3BF511A818}"/>
+    <hyperlink ref="E26" r:id="rId9" xr:uid="{461EAE59-6B89-4B06-BC7F-5D62D70EDCD6}"/>
+    <hyperlink ref="D23" r:id="rId10" xr:uid="{9FC614FC-A94D-4784-8E8F-DFD619EA88C0}"/>
+    <hyperlink ref="D22" r:id="rId11" xr:uid="{0B29772C-F7FE-40CC-A257-2848F4518174}"/>
+    <hyperlink ref="E20" r:id="rId12" xr:uid="{C474B74F-3E03-433F-BC35-18768486A4FB}"/>
+    <hyperlink ref="E19" r:id="rId13" xr:uid="{209BE10C-36A4-4475-BDA6-365C34A7A7B4}"/>
+    <hyperlink ref="D18" r:id="rId14" xr:uid="{D908A389-6872-41E0-B81F-166FB55D55A3}"/>
+    <hyperlink ref="D17" r:id="rId15" xr:uid="{1BBDB9F5-EA33-4B8D-A13B-752105B1611A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId16"/>

--- a/data/posts.xlsx
+++ b/data/posts.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1E243A0-8538-4AA1-AC32-67076F5499D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B530E44-0C69-443A-9283-00E2EA91EBC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="137">
   <si>
     <t>date</t>
   </si>
@@ -436,6 +436,12 @@
   </si>
   <si>
     <t>https://www.linkedin.com/posts/kasparrufibach_phd-statistics-mathematics-ugcPost-7462018304820428800-dPBW?utm_source=share&amp;utm_medium=member_desktop&amp;rcm=ACoAAAQJ2qsB_r_XsYhAPWyf_WQeC5V6NOcbIXo</t>
+  </si>
+  <si>
+    <t>https://lnkd.in/p/e529t2Kj</t>
+  </si>
+  <si>
+    <t>One the two trial paradigm</t>
   </si>
 </sst>
 </file>
@@ -778,17 +784,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E65"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E66"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="106.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="106.7265625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="223" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="99.42578125" customWidth="1"/>
+    <col min="5" max="5" width="99.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -805,147 +811,147 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
+        <v>46234</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2">
         <v>46191</v>
       </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
         <v>133</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D3" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
+    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="2">
         <v>46157</v>
       </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
         <v>132</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D4" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
+    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="2">
         <v>46148</v>
       </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
         <v>120</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D5" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
+    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="2">
         <v>46145</v>
       </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
         <v>119</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D6" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
+    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2">
         <v>46084</v>
       </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
         <v>116</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D7" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
+    <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="2">
         <v>46030</v>
       </c>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
         <v>114</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D8" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
+    <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="2">
         <v>46001</v>
       </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" t="s">
         <v>113</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D9" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
+    <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="2">
         <v>45992</v>
       </c>
-      <c r="B9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" t="s">
         <v>109</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D10" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
+    <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="2">
         <v>45989</v>
       </c>
-      <c r="B10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" t="s">
         <v>108</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
-        <v>45964</v>
-      </c>
-      <c r="B11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" t="s">
-        <v>104</v>
-      </c>
-      <c r="D11" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>45964</v>
       </c>
@@ -953,768 +959,782 @@
         <v>13</v>
       </c>
       <c r="C12" t="s">
+        <v>104</v>
+      </c>
+      <c r="D12" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="2">
+        <v>45964</v>
+      </c>
+      <c r="B13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" t="s">
         <v>103</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D13" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
+    <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="2">
         <v>45959</v>
       </c>
-      <c r="B13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="B14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" t="s">
         <v>107</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D14" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
+    <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="2">
         <v>45956</v>
       </c>
-      <c r="B14" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="B15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" t="s">
         <v>100</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D15" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
+    <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="2">
         <v>45941</v>
       </c>
-      <c r="B15" t="s">
-        <v>13</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="B16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" t="s">
         <v>98</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D16" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2">
+    <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="2">
         <v>45927</v>
       </c>
-      <c r="B16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="B17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" t="s">
         <v>97</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D17" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
+    <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="2">
         <v>45871</v>
       </c>
-      <c r="B17" t="s">
-        <v>13</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="B18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" t="s">
         <v>94</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D18" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
+    <row r="19" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="2">
         <v>45868</v>
       </c>
-      <c r="B18" t="s">
-        <v>13</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="B19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" t="s">
         <v>93</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D19" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
+    <row r="20" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="2">
         <v>45855</v>
       </c>
-      <c r="B19" t="s">
-        <v>13</v>
-      </c>
-      <c r="C19" s="5" t="s">
+      <c r="B20" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D20" t="s">
         <v>90</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E20" s="4" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
+    <row r="21" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="2">
         <v>45784</v>
       </c>
-      <c r="B20" t="s">
-        <v>13</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="B21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" t="s">
         <v>87</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D21" t="s">
         <v>88</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E21" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
+    <row r="22" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="2">
         <v>45725</v>
       </c>
-      <c r="B21" t="s">
-        <v>13</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="B22" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" t="s">
         <v>85</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D22" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2">
+    <row r="23" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="2">
         <v>45696</v>
       </c>
-      <c r="B22" t="s">
-        <v>13</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="B23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" t="s">
         <v>84</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D23" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
+    <row r="24" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="2">
         <v>45686</v>
       </c>
-      <c r="B23" t="s">
-        <v>13</v>
-      </c>
-      <c r="C23" t="s">
+      <c r="B24" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" t="s">
         <v>81</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D24" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2">
+    <row r="25" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="2">
         <v>45623</v>
       </c>
-      <c r="B24" t="s">
-        <v>13</v>
-      </c>
-      <c r="C24" t="s">
+      <c r="B25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" t="s">
         <v>80</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D25" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="2">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" s="2">
         <v>45584</v>
       </c>
-      <c r="B25" t="s">
-        <v>13</v>
-      </c>
-      <c r="C25" t="s">
+      <c r="B26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" t="s">
         <v>78</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D26" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="2">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" s="2">
         <v>45568</v>
       </c>
-      <c r="B26" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" s="5" t="s">
+      <c r="B27" t="s">
+        <v>13</v>
+      </c>
+      <c r="C27" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D27" t="s">
         <v>74</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E27" s="4" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="2">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28" s="2">
         <v>45565</v>
       </c>
-      <c r="B27" t="s">
-        <v>13</v>
-      </c>
-      <c r="C27" t="s">
+      <c r="B28" t="s">
+        <v>13</v>
+      </c>
+      <c r="C28" t="s">
         <v>73</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D28" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="2">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" s="2">
         <v>45557</v>
       </c>
-      <c r="B28" t="s">
-        <v>13</v>
-      </c>
-      <c r="C28" t="s">
+      <c r="B29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" t="s">
         <v>70</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D29" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="2">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" s="2">
         <v>45537</v>
       </c>
-      <c r="B29" t="s">
-        <v>13</v>
-      </c>
-      <c r="C29" t="s">
+      <c r="B30" t="s">
+        <v>13</v>
+      </c>
+      <c r="C30" t="s">
         <v>68</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D30" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="2">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" s="2">
         <v>45533</v>
       </c>
-      <c r="B30" t="s">
-        <v>13</v>
-      </c>
-      <c r="C30" t="s">
+      <c r="B31" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" t="s">
         <v>66</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D31" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="2">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32" s="2">
         <v>45509</v>
       </c>
-      <c r="B31" t="s">
-        <v>13</v>
-      </c>
-      <c r="C31" t="s">
+      <c r="B32" t="s">
+        <v>13</v>
+      </c>
+      <c r="C32" t="s">
         <v>62</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D32" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="2">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A33" s="2">
         <v>45504</v>
       </c>
-      <c r="B32" t="s">
-        <v>13</v>
-      </c>
-      <c r="C32" t="s">
+      <c r="B33" t="s">
+        <v>13</v>
+      </c>
+      <c r="C33" t="s">
         <v>64</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D33" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="2">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A34" s="2">
         <v>45490</v>
       </c>
-      <c r="B33" t="s">
-        <v>13</v>
-      </c>
-      <c r="C33" t="s">
+      <c r="B34" t="s">
+        <v>13</v>
+      </c>
+      <c r="C34" t="s">
         <v>60</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D34" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="2">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A35" s="2">
         <v>45482</v>
       </c>
-      <c r="B34" t="s">
-        <v>13</v>
-      </c>
-      <c r="C34" t="s">
+      <c r="B35" t="s">
+        <v>13</v>
+      </c>
+      <c r="C35" t="s">
         <v>58</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D35" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="2">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A36" s="2">
         <v>45473</v>
       </c>
-      <c r="B35" t="s">
-        <v>13</v>
-      </c>
-      <c r="C35" t="s">
+      <c r="B36" t="s">
+        <v>13</v>
+      </c>
+      <c r="C36" t="s">
         <v>56</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D36" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="2">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A37" s="2">
         <v>45443</v>
       </c>
-      <c r="B36" t="s">
-        <v>13</v>
-      </c>
-      <c r="C36" t="s">
+      <c r="B37" t="s">
+        <v>13</v>
+      </c>
+      <c r="C37" t="s">
         <v>54</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D37" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="2">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A38" s="2">
         <v>45357</v>
       </c>
-      <c r="B37" t="s">
-        <v>13</v>
-      </c>
-      <c r="C37" t="s">
+      <c r="B38" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" t="s">
         <v>51</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D38" t="s">
         <v>52</v>
       </c>
-      <c r="E37" t="s">
+      <c r="E38" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="2">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A39" s="2">
         <v>45352</v>
       </c>
-      <c r="B38" t="s">
-        <v>13</v>
-      </c>
-      <c r="C38" t="s">
+      <c r="B39" t="s">
+        <v>13</v>
+      </c>
+      <c r="C39" t="s">
         <v>50</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D39" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="2">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A40" s="2">
         <v>45240</v>
       </c>
-      <c r="B39" t="s">
-        <v>13</v>
-      </c>
-      <c r="C39" t="s">
+      <c r="B40" t="s">
+        <v>13</v>
+      </c>
+      <c r="C40" t="s">
         <v>48</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D40" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="2">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A41" s="2">
         <v>45212</v>
       </c>
-      <c r="B40" t="s">
-        <v>13</v>
-      </c>
-      <c r="C40" t="s">
+      <c r="B41" t="s">
+        <v>13</v>
+      </c>
+      <c r="C41" t="s">
         <v>44</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D41" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="2">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A42" s="2">
         <v>45211</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C41" t="s">
+      <c r="B42" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C42" t="s">
         <v>42</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D42" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="2">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A43" s="2">
         <v>45147</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C42" t="s">
+      <c r="B43" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C43" t="s">
         <v>38</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D43" t="s">
         <v>39</v>
       </c>
-      <c r="E42" t="s">
+      <c r="E43" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="2">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A44" s="2">
         <v>45143</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C43" t="s">
+      <c r="B44" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C44" t="s">
         <v>35</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D44" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A44" s="2">
+    <row r="45" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A45" s="2">
         <v>45119</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C44" s="3" t="s">
+      <c r="B45" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="D45" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="2">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A46" s="2">
         <v>45113</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C45" t="s">
+      <c r="B46" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C46" t="s">
         <v>17</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="D46" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="2">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A47" s="2">
         <v>45112</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C46" t="s">
+      <c r="B47" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C47" t="s">
         <v>19</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="D47" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="2">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A48" s="2">
         <v>45083</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C47" t="s">
+      <c r="B48" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C48" t="s">
         <v>123</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D48" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="2">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49" s="2">
         <v>45082</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C48" t="s">
+      <c r="B49" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C49" t="s">
         <v>122</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D49" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="2">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50" s="2">
         <v>45018</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C49" t="s">
+      <c r="B50" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50" t="s">
         <v>45</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="D50" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="2">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51" s="2">
         <v>45014</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C50" t="s">
+      <c r="B51" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C51" t="s">
         <v>124</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D51" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="2">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52" s="2">
         <v>44992</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C51" t="s">
+      <c r="B52" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C52" t="s">
         <v>125</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D52" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="2">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53" s="2">
         <v>44959</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C52" t="s">
+      <c r="B53" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C53" t="s">
         <v>126</v>
       </c>
-      <c r="D52" t="s">
+      <c r="D53" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="2">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54" s="2">
         <v>44930</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C53" t="s">
+      <c r="B54" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C54" t="s">
         <v>127</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D54" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="2">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55" s="2">
         <v>44897</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C54" t="s">
+      <c r="B55" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C55" t="s">
         <v>128</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="D55" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="2">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56" s="2">
         <v>44682</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C55" t="s">
+      <c r="B56" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C56" t="s">
         <v>129</v>
       </c>
-      <c r="D55" t="s">
+      <c r="D56" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="2">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57" s="2">
         <v>44601</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C56" t="s">
+      <c r="B57" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C57" t="s">
         <v>130</v>
       </c>
-      <c r="D56" t="s">
+      <c r="D57" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="2">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58" s="2">
         <v>44725</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C57" t="s">
-        <v>31</v>
-      </c>
-      <c r="D57" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="2">
-        <v>44723</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C58" t="s">
-        <v>33</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="D58" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" s="2">
-        <v>44326</v>
+        <v>44723</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C59" t="s">
-        <v>29</v>
-      </c>
-      <c r="D59" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
-        <v>44265</v>
+        <v>44326</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C60" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D60" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" s="2">
-        <v>44148</v>
+        <v>44265</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C61" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D61" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
-        <v>44146</v>
+        <v>44148</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C62" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D62" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" s="2">
-        <v>44144</v>
+        <v>44146</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C63" t="s">
+        <v>23</v>
+      </c>
+      <c r="D63" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A64" s="2">
+        <v>44144</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C64" t="s">
         <v>22</v>
       </c>
-      <c r="D63" t="s">
+      <c r="D64" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B64" s="2"/>
-    </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B65" s="2"/>
     </row>
+    <row r="66" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B66" s="2"/>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A34:D54">
-    <sortCondition ref="B34:B54"/>
-    <sortCondition descending="1" ref="A34:A54"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A35:D55">
+    <sortCondition ref="B35:B55"/>
+    <sortCondition descending="1" ref="A35:A55"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="D54" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="D44" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="D45" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="D46" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="D58" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="D41" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="D49" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="D33" r:id="rId8" xr:uid="{FA3531C4-3B8B-4257-B20B-BB3BF511A818}"/>
-    <hyperlink ref="E26" r:id="rId9" xr:uid="{461EAE59-6B89-4B06-BC7F-5D62D70EDCD6}"/>
-    <hyperlink ref="D23" r:id="rId10" xr:uid="{9FC614FC-A94D-4784-8E8F-DFD619EA88C0}"/>
-    <hyperlink ref="D22" r:id="rId11" xr:uid="{0B29772C-F7FE-40CC-A257-2848F4518174}"/>
-    <hyperlink ref="E20" r:id="rId12" xr:uid="{C474B74F-3E03-433F-BC35-18768486A4FB}"/>
-    <hyperlink ref="E19" r:id="rId13" xr:uid="{209BE10C-36A4-4475-BDA6-365C34A7A7B4}"/>
-    <hyperlink ref="D18" r:id="rId14" xr:uid="{D908A389-6872-41E0-B81F-166FB55D55A3}"/>
-    <hyperlink ref="D17" r:id="rId15" xr:uid="{1BBDB9F5-EA33-4B8D-A13B-752105B1611A}"/>
+    <hyperlink ref="D55" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="D45" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="D46" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="D47" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="D59" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="D42" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="D50" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="D34" r:id="rId8" xr:uid="{FA3531C4-3B8B-4257-B20B-BB3BF511A818}"/>
+    <hyperlink ref="E27" r:id="rId9" xr:uid="{461EAE59-6B89-4B06-BC7F-5D62D70EDCD6}"/>
+    <hyperlink ref="D24" r:id="rId10" xr:uid="{9FC614FC-A94D-4784-8E8F-DFD619EA88C0}"/>
+    <hyperlink ref="D23" r:id="rId11" xr:uid="{0B29772C-F7FE-40CC-A257-2848F4518174}"/>
+    <hyperlink ref="E21" r:id="rId12" xr:uid="{C474B74F-3E03-433F-BC35-18768486A4FB}"/>
+    <hyperlink ref="E20" r:id="rId13" xr:uid="{209BE10C-36A4-4475-BDA6-365C34A7A7B4}"/>
+    <hyperlink ref="D19" r:id="rId14" xr:uid="{D908A389-6872-41E0-B81F-166FB55D55A3}"/>
+    <hyperlink ref="D18" r:id="rId15" xr:uid="{1BBDB9F5-EA33-4B8D-A13B-752105B1611A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId16"/>

--- a/data/posts.xlsx
+++ b/data/posts.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B530E44-0C69-443A-9283-00E2EA91EBC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D91A1FCB-3228-4DBF-AEB8-245C3EC5C642}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3040" yWindow="3040" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="139">
   <si>
     <t>date</t>
   </si>
@@ -442,6 +442,12 @@
   </si>
   <si>
     <t>One the two trial paradigm</t>
+  </si>
+  <si>
+    <t>https://lnkd.in/p/eqvd5i5r</t>
+  </si>
+  <si>
+    <t>Debating culture of the EFSPI workshop</t>
   </si>
 </sst>
 </file>
@@ -784,7 +790,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.1796875" bestFit="1" customWidth="1"/>
@@ -813,156 +819,156 @@
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
-        <v>46234</v>
+        <v>46256</v>
       </c>
       <c r="B2" t="s">
         <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
-        <v>46191</v>
+        <v>46232</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
-        <v>46157</v>
+        <v>46191</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D4" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
-        <v>46148</v>
+        <v>46157</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="D5" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
-        <v>46145</v>
+        <v>46148</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
-        <v>46084</v>
+        <v>46145</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
-        <v>46030</v>
+        <v>46084</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D8" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
-        <v>46001</v>
+        <v>46030</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D9" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
-        <v>45992</v>
+        <v>46001</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>108</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
+      </c>
+      <c r="D11" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
-        <v>45964</v>
+        <v>45989</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>104</v>
-      </c>
-      <c r="D12" t="s">
-        <v>105</v>
+        <v>108</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -973,768 +979,782 @@
         <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D13" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
-        <v>45959</v>
+        <v>45964</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D14" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
-        <v>45956</v>
+        <v>45959</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="D15" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
-        <v>45941</v>
+        <v>45956</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
       </c>
       <c r="C16" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D16" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
-        <v>45927</v>
+        <v>45941</v>
       </c>
       <c r="B17" t="s">
         <v>13</v>
       </c>
       <c r="C17" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D17" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
-        <v>45871</v>
+        <v>45927</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
       </c>
       <c r="C18" t="s">
-        <v>94</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="D18" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
-        <v>45868</v>
+        <v>45871</v>
       </c>
       <c r="B19" t="s">
         <v>13</v>
       </c>
       <c r="C19" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
-        <v>45855</v>
+        <v>45868</v>
       </c>
       <c r="B20" t="s">
         <v>13</v>
       </c>
-      <c r="C20" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="D20" t="s">
-        <v>90</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>75</v>
+      <c r="C20" t="s">
+        <v>93</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
-        <v>45784</v>
+        <v>45855</v>
       </c>
       <c r="B21" t="s">
         <v>13</v>
       </c>
-      <c r="C21" t="s">
-        <v>87</v>
+      <c r="C21" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="D21" t="s">
-        <v>88</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
-        <v>45725</v>
+        <v>45784</v>
       </c>
       <c r="B22" t="s">
         <v>13</v>
       </c>
       <c r="C22" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D22" t="s">
-        <v>86</v>
+        <v>88</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
-        <v>45696</v>
+        <v>45725</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
       </c>
       <c r="C23" t="s">
-        <v>84</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
+      </c>
+      <c r="D23" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
-        <v>45686</v>
+        <v>45696</v>
       </c>
       <c r="B24" t="s">
         <v>13</v>
       </c>
       <c r="C24" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
+        <v>45686</v>
+      </c>
+      <c r="B25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" t="s">
+        <v>81</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="2">
         <v>45623</v>
       </c>
-      <c r="B25" t="s">
-        <v>13</v>
-      </c>
-      <c r="C25" t="s">
+      <c r="B26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" t="s">
         <v>80</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D26" t="s">
         <v>79</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A26" s="2">
-        <v>45584</v>
-      </c>
-      <c r="B26" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" t="s">
-        <v>78</v>
-      </c>
-      <c r="D26" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
-        <v>45568</v>
+        <v>45584</v>
       </c>
       <c r="B27" t="s">
         <v>13</v>
       </c>
-      <c r="C27" s="5" t="s">
-        <v>76</v>
+      <c r="C27" t="s">
+        <v>78</v>
       </c>
       <c r="D27" t="s">
-        <v>74</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
-        <v>45565</v>
+        <v>45568</v>
       </c>
       <c r="B28" t="s">
         <v>13</v>
       </c>
-      <c r="C28" t="s">
-        <v>73</v>
+      <c r="C28" s="5" t="s">
+        <v>76</v>
       </c>
       <c r="D28" t="s">
-        <v>72</v>
+        <v>74</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
-        <v>45557</v>
+        <v>45565</v>
       </c>
       <c r="B29" t="s">
         <v>13</v>
       </c>
       <c r="C29" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D29" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
-        <v>45537</v>
+        <v>45557</v>
       </c>
       <c r="B30" t="s">
         <v>13</v>
       </c>
       <c r="C30" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D30" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
-        <v>45533</v>
+        <v>45537</v>
       </c>
       <c r="B31" t="s">
         <v>13</v>
       </c>
       <c r="C31" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D31" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
-        <v>45509</v>
+        <v>45533</v>
       </c>
       <c r="B32" t="s">
         <v>13</v>
       </c>
       <c r="C32" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D32" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
-        <v>45504</v>
+        <v>45509</v>
       </c>
       <c r="B33" t="s">
         <v>13</v>
       </c>
       <c r="C33" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D33" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
-        <v>45490</v>
+        <v>45504</v>
       </c>
       <c r="B34" t="s">
         <v>13</v>
       </c>
       <c r="C34" t="s">
-        <v>60</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
+      </c>
+      <c r="D34" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
-        <v>45482</v>
+        <v>45490</v>
       </c>
       <c r="B35" t="s">
         <v>13</v>
       </c>
       <c r="C35" t="s">
-        <v>58</v>
-      </c>
-      <c r="D35" t="s">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
-        <v>45473</v>
+        <v>45482</v>
       </c>
       <c r="B36" t="s">
         <v>13</v>
       </c>
       <c r="C36" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D36" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
-        <v>45443</v>
+        <v>45473</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
       </c>
       <c r="C37" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D37" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
-        <v>45357</v>
+        <v>45443</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
       </c>
       <c r="C38" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D38" t="s">
-        <v>52</v>
-      </c>
-      <c r="E38" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
-        <v>45352</v>
+        <v>45357</v>
       </c>
       <c r="B39" t="s">
         <v>13</v>
       </c>
       <c r="C39" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D39" t="s">
-        <v>49</v>
+        <v>52</v>
+      </c>
+      <c r="E39" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
-        <v>45240</v>
+        <v>45352</v>
       </c>
       <c r="B40" t="s">
         <v>13</v>
       </c>
       <c r="C40" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D40" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
-        <v>45212</v>
+        <v>45240</v>
       </c>
       <c r="B41" t="s">
         <v>13</v>
       </c>
       <c r="C41" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D41" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
-        <v>45211</v>
-      </c>
-      <c r="B42" s="2" t="s">
+        <v>45212</v>
+      </c>
+      <c r="B42" t="s">
         <v>13</v>
       </c>
       <c r="C42" t="s">
-        <v>42</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
+      </c>
+      <c r="D42" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
-        <v>45147</v>
+        <v>45211</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C43" t="s">
-        <v>38</v>
-      </c>
-      <c r="D43" t="s">
-        <v>39</v>
-      </c>
-      <c r="E43" t="s">
-        <v>40</v>
+        <v>42</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
+        <v>45147</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C44" t="s">
+        <v>38</v>
+      </c>
+      <c r="D44" t="s">
+        <v>39</v>
+      </c>
+      <c r="E44" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A45" s="2">
         <v>45143</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C44" t="s">
+      <c r="B45" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C45" t="s">
         <v>35</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D45" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A45" s="2">
+    <row r="46" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A46" s="2">
         <v>45119</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C45" s="3" t="s">
+      <c r="B46" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="D46" s="1" t="s">
         <v>14</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A46" s="2">
-        <v>45113</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C46" t="s">
-        <v>17</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
-        <v>45112</v>
+        <v>45113</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C47" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
-        <v>45083</v>
+        <v>45112</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C48" t="s">
-        <v>123</v>
-      </c>
-      <c r="D48" t="s">
-        <v>3</v>
+        <v>19</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
-        <v>45082</v>
+        <v>45083</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C49" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D49" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
-        <v>45018</v>
+        <v>45082</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C50" t="s">
-        <v>45</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>46</v>
+        <v>122</v>
+      </c>
+      <c r="D50" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
-        <v>45014</v>
+        <v>45018</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C51" t="s">
-        <v>124</v>
-      </c>
-      <c r="D51" t="s">
-        <v>5</v>
+        <v>45</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
-        <v>44992</v>
+        <v>45014</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C52" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D52" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" s="2">
-        <v>44959</v>
+        <v>44992</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C53" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D53" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
-        <v>44930</v>
+        <v>44959</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C54" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D54" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" s="2">
-        <v>44897</v>
+        <v>44930</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C55" t="s">
-        <v>128</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>11</v>
+        <v>127</v>
+      </c>
+      <c r="D55" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
-        <v>44682</v>
+        <v>44897</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C56" t="s">
-        <v>129</v>
-      </c>
-      <c r="D56" t="s">
-        <v>9</v>
+        <v>128</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" s="2">
-        <v>44601</v>
+        <v>44682</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C57" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D57" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
-        <v>44725</v>
+        <v>44601</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C58" t="s">
-        <v>31</v>
+        <v>130</v>
       </c>
       <c r="D58" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" s="2">
-        <v>44723</v>
+        <v>44725</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C59" t="s">
-        <v>33</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
+      </c>
+      <c r="D59" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
-        <v>44326</v>
+        <v>44723</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C60" t="s">
-        <v>29</v>
-      </c>
-      <c r="D60" t="s">
-        <v>30</v>
+        <v>33</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" s="2">
-        <v>44265</v>
+        <v>44326</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C61" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D61" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
-        <v>44148</v>
+        <v>44265</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C62" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D62" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" s="2">
-        <v>44146</v>
+        <v>44148</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C63" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D63" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" s="2">
-        <v>44144</v>
+        <v>44146</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C64" t="s">
+        <v>23</v>
+      </c>
+      <c r="D64" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A65" s="2">
+        <v>44144</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C65" t="s">
         <v>22</v>
       </c>
-      <c r="D64" t="s">
+      <c r="D65" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B65" s="2"/>
-    </row>
-    <row r="66" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B66" s="2"/>
     </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B67" s="2"/>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A35:D55">
-    <sortCondition ref="B35:B55"/>
-    <sortCondition descending="1" ref="A35:A55"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A36:D56">
+    <sortCondition ref="B36:B56"/>
+    <sortCondition descending="1" ref="A36:A56"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="D55" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="D45" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="D46" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="D47" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="D59" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="D42" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="D50" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="D34" r:id="rId8" xr:uid="{FA3531C4-3B8B-4257-B20B-BB3BF511A818}"/>
-    <hyperlink ref="E27" r:id="rId9" xr:uid="{461EAE59-6B89-4B06-BC7F-5D62D70EDCD6}"/>
-    <hyperlink ref="D24" r:id="rId10" xr:uid="{9FC614FC-A94D-4784-8E8F-DFD619EA88C0}"/>
-    <hyperlink ref="D23" r:id="rId11" xr:uid="{0B29772C-F7FE-40CC-A257-2848F4518174}"/>
-    <hyperlink ref="E21" r:id="rId12" xr:uid="{C474B74F-3E03-433F-BC35-18768486A4FB}"/>
-    <hyperlink ref="E20" r:id="rId13" xr:uid="{209BE10C-36A4-4475-BDA6-365C34A7A7B4}"/>
-    <hyperlink ref="D19" r:id="rId14" xr:uid="{D908A389-6872-41E0-B81F-166FB55D55A3}"/>
-    <hyperlink ref="D18" r:id="rId15" xr:uid="{1BBDB9F5-EA33-4B8D-A13B-752105B1611A}"/>
+    <hyperlink ref="D56" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="D46" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="D47" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="D48" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="D60" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="D43" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="D51" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="D35" r:id="rId8" xr:uid="{FA3531C4-3B8B-4257-B20B-BB3BF511A818}"/>
+    <hyperlink ref="E28" r:id="rId9" xr:uid="{461EAE59-6B89-4B06-BC7F-5D62D70EDCD6}"/>
+    <hyperlink ref="D25" r:id="rId10" xr:uid="{9FC614FC-A94D-4784-8E8F-DFD619EA88C0}"/>
+    <hyperlink ref="D24" r:id="rId11" xr:uid="{0B29772C-F7FE-40CC-A257-2848F4518174}"/>
+    <hyperlink ref="E22" r:id="rId12" xr:uid="{C474B74F-3E03-433F-BC35-18768486A4FB}"/>
+    <hyperlink ref="E21" r:id="rId13" xr:uid="{209BE10C-36A4-4475-BDA6-365C34A7A7B4}"/>
+    <hyperlink ref="D20" r:id="rId14" xr:uid="{D908A389-6872-41E0-B81F-166FB55D55A3}"/>
+    <hyperlink ref="D19" r:id="rId15" xr:uid="{1BBDB9F5-EA33-4B8D-A13B-752105B1611A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId16"/>
